--- a/TableExporter/excel/type_template.xlsx
+++ b/TableExporter/excel/type_template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ArrowPopBall\TableExporter\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WSB_BalloonOut\TableExporter\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A2CA8DB-4B62-420C-8A38-94FB85069F4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D6DBADD-7FB3-4ABF-849C-85A355B2E4E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1215" yWindow="3435" windowWidth="21600" windowHeight="11295" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="common_types" sheetId="11" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1465" uniqueCount="546">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1405" uniqueCount="527">
   <si>
     <t>desc1</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -971,22 +971,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>FreezeTimer</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Hammer</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ColorVacuum</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Rocket</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>NoAds</t>
   </si>
   <si>
@@ -994,24 +978,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>AdditionalTime</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ReverseGate</t>
-  </si>
-  <si>
-    <t>ReverseGate</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>AdditionalBombTime</t>
-  </si>
-  <si>
-    <t>AdditionalBombTime</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>AdsFree</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1036,10 +1002,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>InfiniteHeart</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Item_Type</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1636,10 +1598,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>DoorLockMove</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>BLOCK_GIMMICK_CATEGORY</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1688,22 +1646,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>AddTimer</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>AddTimer 부스터</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>RandomRocket</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>RandomRocket 부스터</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>OBS</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1890,42 +1832,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>ChangeGateColor</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ChangeGateSize</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>AddDynamiteCount</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ReverseCurtain</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SwitchGateColor</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>JumpingSingleDoorMove</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Chain</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>InfiniteAddTimer</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>InfiniteRandomRocket</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>PickOne_4</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2196,6 +2106,22 @@
   </si>
   <si>
     <t>시즌10</t>
+  </si>
+  <si>
+    <t>Undo</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hint</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TripleArrow</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DartArrow</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2799,10 +2725,10 @@
         <v>Lobby_StageBlock_Type|0</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="E5" s="9">
         <v>0</v>
@@ -2812,10 +2738,10 @@
         <v>로비 스테이지 블록 | Green</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="J5" s="9"/>
     </row>
@@ -2825,10 +2751,10 @@
         <v>Lobby_StageBlock_Type|1</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="E6" s="9">
         <v>1</v>
@@ -2838,10 +2764,10 @@
         <v>로비 스테이지 블록 | Red</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="J6" s="9"/>
     </row>
@@ -2851,10 +2777,10 @@
         <v>Lobby_StageBlock_Type|2</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="E7" s="9">
         <v>2</v>
@@ -2864,10 +2790,10 @@
         <v>로비 스테이지 블록 | Purple</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="J7" s="9"/>
     </row>
@@ -2877,7 +2803,7 @@
         <v>Gimmick_Unlock_Info_Type|0</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>41</v>
@@ -2890,7 +2816,7 @@
         <v>기믹 언락 안내 | None</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="I8" s="9" t="s">
         <v>41</v>
@@ -2903,10 +2829,10 @@
         <v>Gimmick_Unlock_Info_Type|1</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="E9" s="9">
         <v>1</v>
@@ -2916,10 +2842,10 @@
         <v>기믹 언락 안내 | ArrowBlock</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="J9" s="9"/>
     </row>
@@ -2929,10 +2855,10 @@
         <v>Gimmick_Unlock_Info_Type|2</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="E10" s="9">
         <v>2</v>
@@ -2942,10 +2868,10 @@
         <v>기믹 언락 안내 | LayerBlock</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="J10" s="9"/>
     </row>
@@ -2955,10 +2881,10 @@
         <v>Gimmick_Unlock_Info_Type|3</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="E11" s="9">
         <v>3</v>
@@ -2968,10 +2894,10 @@
         <v>기믹 언락 안내 | IceBlock</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="J11" s="9"/>
     </row>
@@ -2981,10 +2907,10 @@
         <v>Gimmick_Unlock_Info_Type|4</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="E12" s="9">
         <v>4</v>
@@ -2994,10 +2920,10 @@
         <v>기믹 언락 안내 | StarBlock</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="J12" s="9"/>
     </row>
@@ -3007,10 +2933,10 @@
         <v>Gimmick_Unlock_Info_Type|5</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="E13" s="9">
         <v>5</v>
@@ -3020,7 +2946,7 @@
         <v>기믹 언락 안내 | StarGate</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="I13" s="9" t="s">
         <v>153</v>
@@ -3033,10 +2959,10 @@
         <v>Gimmick_Unlock_Info_Type|6</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="E14" s="9">
         <v>6</v>
@@ -3046,10 +2972,10 @@
         <v>기믹 언락 안내 | ChainBlock</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="J14" s="9"/>
     </row>
@@ -3059,10 +2985,10 @@
         <v>Gimmick_Unlock_Info_Type|7</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="E15" s="9">
         <v>7</v>
@@ -3072,10 +2998,10 @@
         <v>기믹 언락 안내 | KeyBlock</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="J15" s="9"/>
     </row>
@@ -3085,10 +3011,10 @@
         <v>Gimmick_Unlock_Info_Type|8</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="E16" s="9">
         <v>8</v>
@@ -3098,10 +3024,10 @@
         <v>기믹 언락 안내 | CombinedBlock</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="J16" s="9"/>
     </row>
@@ -3111,7 +3037,7 @@
         <v>Gimmick_Unlock_Info_Type|9</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="D17" s="9" t="s">
         <v>155</v>
@@ -3124,7 +3050,7 @@
         <v>기믹 언락 안내 | Door</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="I17" s="9" t="s">
         <v>155</v>
@@ -3137,10 +3063,10 @@
         <v>Gimmick_Unlock_Info_Type|10</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="E18" s="9">
         <v>10</v>
@@ -3150,10 +3076,10 @@
         <v>기믹 언락 안내 | BombBlock</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="J18" s="9"/>
     </row>
@@ -3163,10 +3089,10 @@
         <v>Gimmick_Unlock_Info_Type|11</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="E19" s="9">
         <v>11</v>
@@ -3176,10 +3102,10 @@
         <v>기믹 언락 안내 | RopesBlock</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="J19" s="9"/>
     </row>
@@ -3189,10 +3115,10 @@
         <v>Gimmick_Unlock_Info_Type|12</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="E20" s="9">
         <v>12</v>
@@ -3202,10 +3128,10 @@
         <v>기믹 언락 안내 | ScissorsBlock</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="J20" s="9"/>
     </row>
@@ -3215,10 +3141,10 @@
         <v>Gimmick_Unlock_Info_Type|13</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="E21" s="9">
         <v>13</v>
@@ -3228,10 +3154,10 @@
         <v>기믹 언락 안내 | ColorfulPath</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="J21" s="9"/>
     </row>
@@ -3241,10 +3167,10 @@
         <v>Gimmick_Unlock_Info_Type|14</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="E22" s="9">
         <v>14</v>
@@ -3254,10 +3180,10 @@
         <v>기믹 언락 안내 | IceGate</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="J22" s="9"/>
     </row>
@@ -3267,10 +3193,10 @@
         <v>Gimmick_Unlock_Info_Type|15</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="E23" s="9">
         <v>15</v>
@@ -3280,10 +3206,10 @@
         <v>기믹 언락 안내 | MovingDoorLock</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="J23" s="9"/>
     </row>
@@ -3293,10 +3219,10 @@
         <v>Gimmick_Unlock_Info_Type|16</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="E24" s="9">
         <v>16</v>
@@ -3306,10 +3232,10 @@
         <v>기믹 언락 안내 | Crate</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="J24" s="9"/>
     </row>
@@ -3319,10 +3245,10 @@
         <v>Gimmick_Unlock_Info_Type|17</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="E25" s="9">
         <v>17</v>
@@ -3332,10 +3258,10 @@
         <v>기믹 언락 안내 | MovingObstacle</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="J25" s="9"/>
     </row>
@@ -3345,10 +3271,10 @@
         <v>Gimmick_Unlock_Info_Type|18</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="E26" s="9">
         <v>18</v>
@@ -3358,10 +3284,10 @@
         <v>기믹 언락 안내 | ScrewBlock</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="J26" s="9"/>
     </row>
@@ -3371,10 +3297,10 @@
         <v>Gimmick_Unlock_Info_Type|19</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="E27" s="9">
         <v>19</v>
@@ -3384,10 +3310,10 @@
         <v>기믹 언락 안내 | ColorDoor</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="J27" s="9"/>
     </row>
@@ -3397,10 +3323,10 @@
         <v>Gimmick_Unlock_Info_Type|20</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="E28" s="9">
         <v>20</v>
@@ -3410,10 +3336,10 @@
         <v>기믹 언락 안내 | ChainGate</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="J28" s="9"/>
     </row>
@@ -3423,10 +3349,10 @@
         <v>Gimmick_Unlock_Info_Type|21</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="E29" s="9">
         <v>21</v>
@@ -3436,10 +3362,10 @@
         <v>기믹 언락 안내 | GatekeyBlock</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="J29" s="9"/>
     </row>
@@ -3449,10 +3375,10 @@
         <v>Gimmick_Unlock_Info_Type|22</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="E30" s="9">
         <v>22</v>
@@ -3462,10 +3388,10 @@
         <v>기믹 언락 안내 | SizeChangingDoor</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="J30" s="9"/>
     </row>
@@ -3475,10 +3401,10 @@
         <v>Gimmick_Unlock_Info_Type|23</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>393</v>
+        <v>383</v>
       </c>
       <c r="E31" s="9">
         <v>23</v>
@@ -3488,10 +3414,10 @@
         <v>기믹 언락 안내 | CombinedLockedBlock</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="J31" s="9"/>
     </row>
@@ -3501,10 +3427,10 @@
         <v>Gimmick_Unlock_Info_Type|24</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="E32" s="9">
         <v>24</v>
@@ -3514,10 +3440,10 @@
         <v>기믹 언락 안내 | HiddenBlock</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="J32" s="9"/>
     </row>
@@ -3527,10 +3453,10 @@
         <v>Gimmick_Unlock_Info_Type|25</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="E33" s="9">
         <v>25</v>
@@ -3540,10 +3466,10 @@
         <v>기믹 언락 안내 | DynamiteBlock</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="I33" s="9" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="J33" s="9"/>
     </row>
@@ -3553,10 +3479,10 @@
         <v>Gimmick_Unlock_Info_Type|26</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="E34" s="9">
         <v>26</v>
@@ -3566,10 +3492,10 @@
         <v>기믹 언락 안내 | CuratinBlock</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="J34" s="9"/>
     </row>
@@ -3579,10 +3505,10 @@
         <v>Gimmick_Unlock_Info_Type|27</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="E35" s="9">
         <v>27</v>
@@ -3592,10 +3518,10 @@
         <v>기믹 언락 안내 | MoveableCrate</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="I35" s="9" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="J35" s="9"/>
     </row>
@@ -3605,10 +3531,10 @@
         <v>Gimmick_Unlock_Info_Type|28</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="E36" s="9">
         <v>28</v>
@@ -3618,10 +3544,10 @@
         <v>기믹 언락 안내 | ColorSwitchingDoor</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="I36" s="9" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="J36" s="9"/>
     </row>
@@ -3631,10 +3557,10 @@
         <v>Gimmick_Unlock_Info_Type|29</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="E37" s="9">
         <v>29</v>
@@ -3644,10 +3570,10 @@
         <v>기믹 언락 안내 | TimeCapsuleBlock</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="I37" s="9" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="J37" s="9"/>
     </row>
@@ -3657,10 +3583,10 @@
         <v>Gimmick_Unlock_Info_Type|30</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="E38" s="9">
         <v>30</v>
@@ -3670,10 +3596,10 @@
         <v>기믹 언락 안내 | ColorSwitchingBlock</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="I38" s="9" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="J38" s="9"/>
     </row>
@@ -3683,10 +3609,10 @@
         <v>Gimmick_Unlock_Info_Type|31</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>401</v>
+        <v>391</v>
       </c>
       <c r="E39" s="9">
         <v>31</v>
@@ -3696,10 +3622,10 @@
         <v>기믹 언락 안내 | JumpingSingleDoor</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="I39" s="9" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="J39" s="9"/>
     </row>
@@ -3709,10 +3635,10 @@
         <v>Gimmick_Unlock_Info_Category|0</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="E40" s="9">
         <v>0</v>
@@ -3722,10 +3648,10 @@
         <v>기믹 카테고리 | None</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="I40" s="9" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="J40" s="9"/>
     </row>
@@ -3735,10 +3661,10 @@
         <v>Gimmick_Unlock_Info_Category|1</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="E41" s="9">
         <v>1</v>
@@ -3748,10 +3674,10 @@
         <v>기믹 카테고리 | 타일</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="I41" s="9" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="J41" s="9"/>
     </row>
@@ -3761,10 +3687,10 @@
         <v>Gimmick_Unlock_Info_Category|2</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="E42" s="9">
         <v>2</v>
@@ -3774,10 +3700,10 @@
         <v>기믹 카테고리 | 블록</v>
       </c>
       <c r="H42" s="9" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="I42" s="9" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="J42" s="9"/>
     </row>
@@ -3787,10 +3713,10 @@
         <v>Gimmick_Unlock_Info_Category|3</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="E43" s="9">
         <v>3</v>
@@ -3800,10 +3726,10 @@
         <v>기믹 카테고리 | 게이트</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="I43" s="9" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="J43" s="9"/>
     </row>
@@ -5022,10 +4948,10 @@
         <v>Block_GimmickType|0</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="E35" s="12">
         <v>0</v>
@@ -5039,7 +4965,7 @@
         <v>170</v>
       </c>
       <c r="I35" s="12" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="J35" s="9"/>
     </row>
@@ -5052,7 +4978,7 @@
         <v>169</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="E36" s="12">
         <v>1</v>
@@ -5066,7 +4992,7 @@
         <v>170</v>
       </c>
       <c r="I36" s="12" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="J36" s="9"/>
     </row>
@@ -5079,7 +5005,7 @@
         <v>169</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="E37" s="12">
         <v>2</v>
@@ -5093,7 +5019,7 @@
         <v>170</v>
       </c>
       <c r="I37" s="12" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="J37" s="9"/>
     </row>
@@ -5106,7 +5032,7 @@
         <v>169</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="E38" s="12">
         <v>3</v>
@@ -5120,7 +5046,7 @@
         <v>170</v>
       </c>
       <c r="I38" s="12" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="J38" s="9"/>
     </row>
@@ -5133,7 +5059,7 @@
         <v>169</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="E39" s="12">
         <v>4</v>
@@ -5147,7 +5073,7 @@
         <v>170</v>
       </c>
       <c r="I39" s="12" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="J39" s="9"/>
     </row>
@@ -5160,7 +5086,7 @@
         <v>169</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="E40" s="12">
         <v>5</v>
@@ -5174,7 +5100,7 @@
         <v>170</v>
       </c>
       <c r="I40" s="12" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="J40" s="9"/>
     </row>
@@ -5187,7 +5113,7 @@
         <v>169</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="E41" s="12">
         <v>6</v>
@@ -5201,7 +5127,7 @@
         <v>170</v>
       </c>
       <c r="I41" s="12" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="J41" s="9"/>
     </row>
@@ -5214,7 +5140,7 @@
         <v>169</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="E42" s="12">
         <v>7</v>
@@ -5228,7 +5154,7 @@
         <v>170</v>
       </c>
       <c r="I42" s="12" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="J42" s="9"/>
     </row>
@@ -5241,7 +5167,7 @@
         <v>169</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="E43" s="12">
         <v>8</v>
@@ -5255,7 +5181,7 @@
         <v>170</v>
       </c>
       <c r="I43" s="12" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="J43" s="9"/>
     </row>
@@ -5268,7 +5194,7 @@
         <v>169</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="E44" s="12">
         <v>9</v>
@@ -5282,7 +5208,7 @@
         <v>170</v>
       </c>
       <c r="I44" s="12" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="J44" s="9"/>
     </row>
@@ -5295,7 +5221,7 @@
         <v>169</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="E45" s="12">
         <v>10</v>
@@ -5309,7 +5235,7 @@
         <v>170</v>
       </c>
       <c r="I45" s="12" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="J45" s="9"/>
     </row>
@@ -5322,7 +5248,7 @@
         <v>169</v>
       </c>
       <c r="D46" s="12" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="E46" s="12">
         <v>11</v>
@@ -5336,7 +5262,7 @@
         <v>170</v>
       </c>
       <c r="I46" s="12" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="J46" s="9"/>
     </row>
@@ -5349,7 +5275,7 @@
         <v>169</v>
       </c>
       <c r="D47" s="12" t="s">
-        <v>420</v>
+        <v>405</v>
       </c>
       <c r="E47" s="12">
         <v>12</v>
@@ -5363,7 +5289,7 @@
         <v>170</v>
       </c>
       <c r="I47" s="12" t="s">
-        <v>420</v>
+        <v>405</v>
       </c>
       <c r="J47" s="9"/>
     </row>
@@ -5376,7 +5302,7 @@
         <v>169</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="E48" s="12">
         <v>13</v>
@@ -5390,7 +5316,7 @@
         <v>170</v>
       </c>
       <c r="I48" s="12" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="J48" s="9"/>
     </row>
@@ -5403,7 +5329,7 @@
         <v>169</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>439</v>
+        <v>424</v>
       </c>
       <c r="E49" s="12">
         <v>14</v>
@@ -5417,7 +5343,7 @@
         <v>170</v>
       </c>
       <c r="I49" s="12" t="s">
-        <v>439</v>
+        <v>424</v>
       </c>
       <c r="J49" s="9"/>
     </row>
@@ -5430,7 +5356,7 @@
         <v>169</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="E50" s="12">
         <v>15</v>
@@ -5444,7 +5370,7 @@
         <v>170</v>
       </c>
       <c r="I50" s="12" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="J50" s="9"/>
     </row>
@@ -5457,7 +5383,7 @@
         <v>169</v>
       </c>
       <c r="D51" s="12" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="E51" s="12">
         <v>16</v>
@@ -5471,7 +5397,7 @@
         <v>170</v>
       </c>
       <c r="I51" s="12" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="J51" s="9"/>
     </row>
@@ -5484,7 +5410,7 @@
         <v>169</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>492</v>
+        <v>469</v>
       </c>
       <c r="E52" s="12">
         <v>17</v>
@@ -5498,7 +5424,7 @@
         <v>170</v>
       </c>
       <c r="I52" s="12" t="s">
-        <v>492</v>
+        <v>469</v>
       </c>
       <c r="J52" s="9"/>
     </row>
@@ -5511,7 +5437,7 @@
         <v>169</v>
       </c>
       <c r="D53" s="12" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="E53" s="12">
         <v>18</v>
@@ -5525,7 +5451,7 @@
         <v>170</v>
       </c>
       <c r="I53" s="12" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="J53" s="9"/>
     </row>
@@ -5538,7 +5464,7 @@
         <v>169</v>
       </c>
       <c r="D54" s="12" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="E54" s="12">
         <v>19</v>
@@ -5552,7 +5478,7 @@
         <v>170</v>
       </c>
       <c r="I54" s="12" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="J54" s="9"/>
     </row>
@@ -5565,7 +5491,7 @@
         <v>169</v>
       </c>
       <c r="D55" s="12" t="s">
-        <v>494</v>
+        <v>471</v>
       </c>
       <c r="E55" s="12">
         <v>20</v>
@@ -5579,7 +5505,7 @@
         <v>170</v>
       </c>
       <c r="I55" s="12" t="s">
-        <v>494</v>
+        <v>471</v>
       </c>
       <c r="J55" s="9"/>
     </row>
@@ -5592,7 +5518,7 @@
         <v>169</v>
       </c>
       <c r="D56" s="12" t="s">
-        <v>495</v>
+        <v>472</v>
       </c>
       <c r="E56" s="12">
         <v>21</v>
@@ -5606,7 +5532,7 @@
         <v>170</v>
       </c>
       <c r="I56" s="12" t="s">
-        <v>495</v>
+        <v>472</v>
       </c>
       <c r="J56" s="9"/>
     </row>
@@ -5827,7 +5753,7 @@
         <v>157</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="E65" s="9">
         <v>8</v>
@@ -5840,7 +5766,7 @@
         <v>179</v>
       </c>
       <c r="I65" s="11" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="J65" s="9"/>
     </row>
@@ -5853,7 +5779,7 @@
         <v>157</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>421</v>
+        <v>406</v>
       </c>
       <c r="E66" s="9">
         <v>9</v>
@@ -5866,7 +5792,7 @@
         <v>179</v>
       </c>
       <c r="I66" s="11" t="s">
-        <v>421</v>
+        <v>406</v>
       </c>
       <c r="J66" s="9"/>
     </row>
@@ -5879,7 +5805,7 @@
         <v>157</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>443</v>
+        <v>428</v>
       </c>
       <c r="E67" s="9">
         <v>10</v>
@@ -5892,7 +5818,7 @@
         <v>179</v>
       </c>
       <c r="I67" s="11" t="s">
-        <v>443</v>
+        <v>428</v>
       </c>
       <c r="J67" s="9"/>
     </row>
@@ -5905,7 +5831,7 @@
         <v>157</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>444</v>
+        <v>429</v>
       </c>
       <c r="E68" s="9">
         <v>11</v>
@@ -5918,7 +5844,7 @@
         <v>179</v>
       </c>
       <c r="I68" s="11" t="s">
-        <v>444</v>
+        <v>429</v>
       </c>
       <c r="J68" s="9"/>
     </row>
@@ -5983,7 +5909,7 @@
         <v>191</v>
       </c>
       <c r="D71" s="9" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E71" s="9">
         <v>0</v>
@@ -5996,7 +5922,7 @@
         <v>194</v>
       </c>
       <c r="I71" s="9" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="J71" s="9"/>
     </row>
@@ -6321,7 +6247,7 @@
         <v>195</v>
       </c>
       <c r="D84" s="9" t="s">
-        <v>419</v>
+        <v>404</v>
       </c>
       <c r="E84" s="9">
         <v>10</v>
@@ -6334,7 +6260,7 @@
         <v>206</v>
       </c>
       <c r="I84" s="9" t="s">
-        <v>436</v>
+        <v>421</v>
       </c>
       <c r="J84" s="9"/>
     </row>
@@ -6347,7 +6273,7 @@
         <v>195</v>
       </c>
       <c r="D85" s="9" t="s">
-        <v>437</v>
+        <v>422</v>
       </c>
       <c r="E85" s="9">
         <v>11</v>
@@ -6360,7 +6286,7 @@
         <v>206</v>
       </c>
       <c r="I85" s="9" t="s">
-        <v>438</v>
+        <v>423</v>
       </c>
       <c r="J85" s="9"/>
     </row>
@@ -6370,10 +6296,10 @@
         <v>TILE_ROTATION_TYPE|0</v>
       </c>
       <c r="C86" s="9" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="D86" s="9" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="E86" s="9">
         <v>0</v>
@@ -6383,7 +6309,7 @@
         <v>타일 회전 | 0</v>
       </c>
       <c r="H86" s="9" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="I86" s="9">
         <v>0</v>
@@ -6396,10 +6322,10 @@
         <v>TILE_ROTATION_TYPE|1</v>
       </c>
       <c r="C87" s="9" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="D87" s="9" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="E87" s="9">
         <v>1</v>
@@ -6409,7 +6335,7 @@
         <v>타일 회전 | 90</v>
       </c>
       <c r="H87" s="9" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="I87" s="9">
         <v>90</v>
@@ -6422,10 +6348,10 @@
         <v>TILE_ROTATION_TYPE|2</v>
       </c>
       <c r="C88" s="9" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="D88" s="9" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="E88" s="9">
         <v>2</v>
@@ -6435,7 +6361,7 @@
         <v>타일 회전 | 180</v>
       </c>
       <c r="H88" s="9" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="I88" s="9">
         <v>180</v>
@@ -6448,10 +6374,10 @@
         <v>TILE_ROTATION_TYPE|3</v>
       </c>
       <c r="C89" s="9" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="D89" s="9" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="E89" s="9">
         <v>3</v>
@@ -6461,7 +6387,7 @@
         <v>타일 회전 | 270</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="I89" s="9">
         <v>270</v>
@@ -6474,10 +6400,10 @@
         <v>TILE_MAP_DIRECTION|0</v>
       </c>
       <c r="C90" s="9" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="D90" s="9" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="E90" s="9">
         <v>0</v>
@@ -6487,10 +6413,10 @@
         <v>맵툴 사용 | LT</v>
       </c>
       <c r="H90" s="9" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="I90" s="9" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="J90" s="9"/>
     </row>
@@ -6500,10 +6426,10 @@
         <v>TILE_MAP_DIRECTION|1</v>
       </c>
       <c r="C91" s="9" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="D91" s="9" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="E91" s="9">
         <v>1</v>
@@ -6513,10 +6439,10 @@
         <v>맵툴 사용 | T</v>
       </c>
       <c r="H91" s="9" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="I91" s="9" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="J91" s="9"/>
     </row>
@@ -6526,10 +6452,10 @@
         <v>TILE_MAP_DIRECTION|2</v>
       </c>
       <c r="C92" s="9" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="D92" s="9" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="E92" s="9">
         <v>2</v>
@@ -6539,10 +6465,10 @@
         <v>맵툴 사용 | RT</v>
       </c>
       <c r="H92" s="9" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="I92" s="9" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="J92" s="9"/>
     </row>
@@ -6552,10 +6478,10 @@
         <v>TILE_MAP_DIRECTION|3</v>
       </c>
       <c r="C93" s="9" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="D93" s="9" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="E93" s="9">
         <v>3</v>
@@ -6565,10 +6491,10 @@
         <v>맵툴 사용 | LC</v>
       </c>
       <c r="H93" s="9" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="I93" s="9" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="J93" s="9"/>
     </row>
@@ -6578,10 +6504,10 @@
         <v>TILE_MAP_DIRECTION|4</v>
       </c>
       <c r="C94" s="9" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="D94" s="9" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="E94" s="9">
         <v>4</v>
@@ -6591,10 +6517,10 @@
         <v>맵툴 사용 | C</v>
       </c>
       <c r="H94" s="9" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="I94" s="9" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="J94" s="9"/>
     </row>
@@ -6604,10 +6530,10 @@
         <v>TILE_MAP_DIRECTION|5</v>
       </c>
       <c r="C95" s="9" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="D95" s="9" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="E95" s="9">
         <v>5</v>
@@ -6617,10 +6543,10 @@
         <v>맵툴 사용 | RC</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="I95" s="9" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="J95" s="9"/>
     </row>
@@ -6630,10 +6556,10 @@
         <v>TILE_MAP_DIRECTION|6</v>
       </c>
       <c r="C96" s="9" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="D96" s="9" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="E96" s="9">
         <v>6</v>
@@ -6643,10 +6569,10 @@
         <v>맵툴 사용 | LB</v>
       </c>
       <c r="H96" s="9" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="I96" s="9" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="J96" s="9"/>
     </row>
@@ -6656,10 +6582,10 @@
         <v>TILE_MAP_DIRECTION|7</v>
       </c>
       <c r="C97" s="9" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="D97" s="9" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="E97" s="9">
         <v>7</v>
@@ -6669,10 +6595,10 @@
         <v>맵툴 사용 | B</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="I97" s="9" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="J97" s="9"/>
     </row>
@@ -6682,10 +6608,10 @@
         <v>TILE_MAP_DIRECTION|8</v>
       </c>
       <c r="C98" s="9" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="D98" s="9" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="E98" s="9">
         <v>8</v>
@@ -6695,10 +6621,10 @@
         <v>맵툴 사용 | RB</v>
       </c>
       <c r="H98" s="9" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="I98" s="9" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="J98" s="9"/>
     </row>
@@ -6708,7 +6634,7 @@
         <v>Gate_GimmickType|0</v>
       </c>
       <c r="C99" s="9" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="D99" s="9" t="s">
         <v>100</v>
@@ -6721,7 +6647,7 @@
         <v>게이트 기믹 타입 | Normal</v>
       </c>
       <c r="H99" s="9" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="I99" s="9" t="s">
         <v>100</v>
@@ -6734,10 +6660,10 @@
         <v>Gate_GimmickType|1</v>
       </c>
       <c r="C100" s="9" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="D100" s="9" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="E100" s="9">
         <v>1</v>
@@ -6747,10 +6673,10 @@
         <v>게이트 기믹 타입 | Star</v>
       </c>
       <c r="H100" s="9" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="I100" s="9" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="J100" s="9"/>
     </row>
@@ -6760,7 +6686,7 @@
         <v>Gate_GimmickType|2</v>
       </c>
       <c r="C101" s="9" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="D101" s="9" t="s">
         <v>155</v>
@@ -6773,7 +6699,7 @@
         <v>게이트 기믹 타입 | Door</v>
       </c>
       <c r="H101" s="9" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="I101" s="9" t="s">
         <v>155</v>
@@ -6786,10 +6712,10 @@
         <v>Gate_GimmickType|3</v>
       </c>
       <c r="C102" s="9" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="D102" s="9" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="E102" s="9">
         <v>3</v>
@@ -6799,10 +6725,10 @@
         <v>게이트 기믹 타입 | Moving_Door_Lock</v>
       </c>
       <c r="H102" s="9" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="I102" s="9" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="J102" s="9"/>
     </row>
@@ -6812,10 +6738,10 @@
         <v>Gate_GimmickType|4</v>
       </c>
       <c r="C103" s="9" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="D103" s="9" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="E103" s="9">
         <v>4</v>
@@ -6825,10 +6751,10 @@
         <v>게이트 기믹 타입 | IceGate</v>
       </c>
       <c r="H103" s="9" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="I103" s="9" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="J103" s="9"/>
     </row>
@@ -6838,10 +6764,10 @@
         <v>Gate_GimmickType|5</v>
       </c>
       <c r="C104" s="9" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="D104" s="9" t="s">
-        <v>422</v>
+        <v>407</v>
       </c>
       <c r="E104" s="9">
         <v>5</v>
@@ -6851,10 +6777,10 @@
         <v>게이트 기믹 타입 | ColorGate</v>
       </c>
       <c r="H104" s="9" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="I104" s="9" t="s">
-        <v>422</v>
+        <v>407</v>
       </c>
       <c r="J104" s="9"/>
     </row>
@@ -6864,10 +6790,10 @@
         <v>Gate_GimmickType|6</v>
       </c>
       <c r="C105" s="9" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="D105" s="9" t="s">
-        <v>472</v>
+        <v>451</v>
       </c>
       <c r="E105" s="9">
         <v>6</v>
@@ -6877,10 +6803,10 @@
         <v>게이트 기믹 타입 | Chain</v>
       </c>
       <c r="H105" s="9" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="I105" s="9" t="s">
-        <v>472</v>
+        <v>451</v>
       </c>
       <c r="J105" s="9"/>
     </row>
@@ -6890,10 +6816,10 @@
         <v>Gate_GimmickType|7</v>
       </c>
       <c r="C106" s="9" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="D106" s="9" t="s">
-        <v>496</v>
+        <v>473</v>
       </c>
       <c r="E106" s="9">
         <v>7</v>
@@ -6903,10 +6829,10 @@
         <v>게이트 기믹 타입 | SizeChanging</v>
       </c>
       <c r="H106" s="9" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="I106" s="9" t="s">
-        <v>496</v>
+        <v>473</v>
       </c>
       <c r="J106" s="9"/>
     </row>
@@ -6916,10 +6842,10 @@
         <v>Gate_GimmickType|8</v>
       </c>
       <c r="C107" s="9" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="D107" s="9" t="s">
-        <v>495</v>
+        <v>472</v>
       </c>
       <c r="E107" s="9">
         <v>8</v>
@@ -6929,10 +6855,10 @@
         <v>게이트 기믹 타입 | ColorSwitching</v>
       </c>
       <c r="H107" s="9" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="I107" s="9" t="s">
-        <v>495</v>
+        <v>472</v>
       </c>
       <c r="J107" s="9"/>
     </row>
@@ -6942,10 +6868,10 @@
         <v>Gate_GimmickType|9</v>
       </c>
       <c r="C108" s="9" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="D108" s="9" t="s">
-        <v>497</v>
+        <v>474</v>
       </c>
       <c r="E108" s="9">
         <v>9</v>
@@ -6955,10 +6881,10 @@
         <v>게이트 기믹 타입 | JumpingSingle</v>
       </c>
       <c r="H108" s="9" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="I108" s="9" t="s">
-        <v>497</v>
+        <v>474</v>
       </c>
       <c r="J108" s="9"/>
     </row>
@@ -6968,7 +6894,7 @@
         <v>Tile_GimmickType|0</v>
       </c>
       <c r="C109" s="9" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="D109" s="9" t="s">
         <v>100</v>
@@ -6981,7 +6907,7 @@
         <v>타일 기믹 타입 | Normal</v>
       </c>
       <c r="H109" s="9" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="I109" s="9" t="s">
         <v>100</v>
@@ -6994,7 +6920,7 @@
         <v>Tile_GimmickType|1</v>
       </c>
       <c r="C110" s="9" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="D110" s="9" t="s">
         <v>189</v>
@@ -7007,7 +6933,7 @@
         <v>타일 기믹 타입 | Colorful</v>
       </c>
       <c r="H110" s="9" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="I110" s="9" t="s">
         <v>189</v>
@@ -7020,7 +6946,7 @@
         <v>BLOCK_GIMMICK_CATEGORY|0</v>
       </c>
       <c r="C111" s="9" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="D111" s="9" t="s">
         <v>41</v>
@@ -7033,7 +6959,7 @@
         <v>블럭 기믹 카테고리 | None</v>
       </c>
       <c r="H111" s="9" t="s">
-        <v>404</v>
+        <v>393</v>
       </c>
       <c r="I111" s="9" t="s">
         <v>41</v>
@@ -7046,10 +6972,10 @@
         <v>BLOCK_GIMMICK_CATEGORY|1</v>
       </c>
       <c r="C112" s="9" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="D112" s="9" t="s">
-        <v>405</v>
+        <v>394</v>
       </c>
       <c r="E112" s="9">
         <v>1</v>
@@ -7059,10 +6985,10 @@
         <v>블럭 기믹 카테고리 | 특별히 분류 할 필요 없는 기믹</v>
       </c>
       <c r="H112" s="9" t="s">
-        <v>404</v>
+        <v>393</v>
       </c>
       <c r="I112" s="9" t="s">
-        <v>409</v>
+        <v>398</v>
       </c>
       <c r="J112" s="9"/>
     </row>
@@ -7072,10 +6998,10 @@
         <v>BLOCK_GIMMICK_CATEGORY|2</v>
       </c>
       <c r="C113" s="9" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="D113" s="9" t="s">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="E113" s="9">
         <v>2</v>
@@ -7085,10 +7011,10 @@
         <v>블럭 기믹 카테고리 | 블럭이 나눠질 때 복사되면 안되는 기믹</v>
       </c>
       <c r="H113" s="9" t="s">
-        <v>404</v>
+        <v>393</v>
       </c>
       <c r="I113" s="9" t="s">
-        <v>410</v>
+        <v>399</v>
       </c>
       <c r="J113" s="9"/>
     </row>
@@ -7098,10 +7024,10 @@
         <v>BLOCK_GIMMICK_CATEGORY|3</v>
       </c>
       <c r="C114" s="9" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="D114" s="9" t="s">
-        <v>407</v>
+        <v>396</v>
       </c>
       <c r="E114" s="9">
         <v>3</v>
@@ -7111,10 +7037,10 @@
         <v>블럭 기믹 카테고리 | 카운트를 사용하는 기믹</v>
       </c>
       <c r="H114" s="9" t="s">
-        <v>404</v>
+        <v>393</v>
       </c>
       <c r="I114" s="9" t="s">
-        <v>411</v>
+        <v>400</v>
       </c>
       <c r="J114" s="9"/>
     </row>
@@ -7124,10 +7050,10 @@
         <v>BLOCK_GIMMICK_CATEGORY|4</v>
       </c>
       <c r="C115" s="9" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="D115" s="9" t="s">
-        <v>408</v>
+        <v>397</v>
       </c>
       <c r="E115" s="9">
         <v>4</v>
@@ -7137,10 +7063,10 @@
         <v>블럭 기믹 카테고리 | 상태가 변하는 기믹</v>
       </c>
       <c r="H115" s="9" t="s">
-        <v>404</v>
+        <v>393</v>
       </c>
       <c r="I115" s="9" t="s">
-        <v>412</v>
+        <v>401</v>
       </c>
       <c r="J115" s="9"/>
     </row>
@@ -7150,7 +7076,7 @@
         <v>CrateBlock_Type|0</v>
       </c>
       <c r="C116" s="9" t="s">
-        <v>423</v>
+        <v>408</v>
       </c>
       <c r="D116" s="9" t="s">
         <v>180</v>
@@ -7163,7 +7089,7 @@
         <v>Crate 기믹 블록타입 | Square_1x1</v>
       </c>
       <c r="H116" s="9" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
       <c r="I116" s="9" t="s">
         <v>180</v>
@@ -7176,7 +7102,7 @@
         <v>CrateBlock_Type|1</v>
       </c>
       <c r="C117" s="9" t="s">
-        <v>423</v>
+        <v>408</v>
       </c>
       <c r="D117" s="9" t="s">
         <v>181</v>
@@ -7189,10 +7115,10 @@
         <v>Crate 기믹 블록타입 | Square_1x2</v>
       </c>
       <c r="H117" s="9" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
       <c r="I117" s="9" t="s">
-        <v>425</v>
+        <v>410</v>
       </c>
       <c r="J117" s="9"/>
     </row>
@@ -7202,10 +7128,10 @@
         <v>CrateBlock_Type|2</v>
       </c>
       <c r="C118" s="9" t="s">
-        <v>423</v>
+        <v>408</v>
       </c>
       <c r="D118" s="9" t="s">
-        <v>442</v>
+        <v>427</v>
       </c>
       <c r="E118" s="9">
         <v>2</v>
@@ -7215,10 +7141,10 @@
         <v>Crate 기믹 블록타입 | Square_1x3</v>
       </c>
       <c r="H118" s="9" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
       <c r="I118" s="9" t="s">
-        <v>442</v>
+        <v>427</v>
       </c>
       <c r="J118" s="9"/>
     </row>
@@ -7228,7 +7154,7 @@
         <v>CrateBlock_Type|3</v>
       </c>
       <c r="C119" s="9" t="s">
-        <v>423</v>
+        <v>408</v>
       </c>
       <c r="D119" s="9" t="s">
         <v>183</v>
@@ -7241,7 +7167,7 @@
         <v>Crate 기믹 블록타입 | Square_2x2</v>
       </c>
       <c r="H119" s="9" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
       <c r="I119" s="9" t="s">
         <v>183</v>
@@ -7254,10 +7180,10 @@
         <v>CrateBlock_Type|4</v>
       </c>
       <c r="C120" s="9" t="s">
-        <v>423</v>
+        <v>408</v>
       </c>
       <c r="D120" s="9" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="E120" s="9">
         <v>4</v>
@@ -7267,10 +7193,10 @@
         <v>Crate 기믹 블록타입 | Square_2x3</v>
       </c>
       <c r="H120" s="9" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
       <c r="I120" s="9" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="J120" s="9"/>
     </row>
@@ -7280,10 +7206,10 @@
         <v>CrateBlock_Type|5</v>
       </c>
       <c r="C121" s="9" t="s">
-        <v>423</v>
+        <v>408</v>
       </c>
       <c r="D121" s="9" t="s">
-        <v>427</v>
+        <v>412</v>
       </c>
       <c r="E121" s="9">
         <v>5</v>
@@ -7293,10 +7219,10 @@
         <v>Crate 기믹 블록타입 | Square_2x4</v>
       </c>
       <c r="H121" s="9" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
       <c r="I121" s="9" t="s">
-        <v>427</v>
+        <v>412</v>
       </c>
       <c r="J121" s="9"/>
     </row>
@@ -7306,10 +7232,10 @@
         <v>CrateBlock_Type|6</v>
       </c>
       <c r="C122" s="9" t="s">
-        <v>423</v>
+        <v>408</v>
       </c>
       <c r="D122" s="9" t="s">
-        <v>430</v>
+        <v>415</v>
       </c>
       <c r="E122" s="9">
         <v>6</v>
@@ -7319,10 +7245,10 @@
         <v>Crate 기믹 블록타입 | Square_2x5</v>
       </c>
       <c r="H122" s="9" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
       <c r="I122" s="9" t="s">
-        <v>430</v>
+        <v>415</v>
       </c>
       <c r="J122" s="9"/>
     </row>
@@ -7332,10 +7258,10 @@
         <v>CrateBlock_Type|7</v>
       </c>
       <c r="C123" s="9" t="s">
-        <v>423</v>
+        <v>408</v>
       </c>
       <c r="D123" s="9" t="s">
-        <v>429</v>
+        <v>414</v>
       </c>
       <c r="E123" s="9">
         <v>7</v>
@@ -7345,10 +7271,10 @@
         <v>Crate 기믹 블록타입 | Square_3x3</v>
       </c>
       <c r="H123" s="9" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
       <c r="I123" s="9" t="s">
-        <v>429</v>
+        <v>414</v>
       </c>
       <c r="J123" s="9"/>
     </row>
@@ -7358,10 +7284,10 @@
         <v>CrateBlock_Type|8</v>
       </c>
       <c r="C124" s="9" t="s">
-        <v>423</v>
+        <v>408</v>
       </c>
       <c r="D124" s="9" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="E124" s="9">
         <v>8</v>
@@ -7371,10 +7297,10 @@
         <v>Crate 기믹 블록타입 | Square_3x4</v>
       </c>
       <c r="H124" s="9" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
       <c r="I124" s="9" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="J124" s="9"/>
     </row>
@@ -7384,7 +7310,7 @@
         <v>CrateBlock_Type|9</v>
       </c>
       <c r="C125" s="9" t="s">
-        <v>423</v>
+        <v>408</v>
       </c>
       <c r="D125" s="9" t="s">
         <v>184</v>
@@ -7397,7 +7323,7 @@
         <v>Crate 기믹 블록타입 | Corner_2x2</v>
       </c>
       <c r="H125" s="9" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
       <c r="I125" s="9" t="s">
         <v>184</v>
@@ -7410,7 +7336,7 @@
         <v>CrateBlock_Type|10</v>
       </c>
       <c r="C126" s="9" t="s">
-        <v>423</v>
+        <v>408</v>
       </c>
       <c r="D126" s="9" t="s">
         <v>187</v>
@@ -7423,7 +7349,7 @@
         <v>Crate 기믹 블록타입 | Corner_2x3</v>
       </c>
       <c r="H126" s="9" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
       <c r="I126" s="9" t="s">
         <v>187</v>
@@ -7436,10 +7362,10 @@
         <v>CrateBlock_Type|11</v>
       </c>
       <c r="C127" s="9" t="s">
-        <v>423</v>
+        <v>408</v>
       </c>
       <c r="D127" s="9" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="E127" s="9">
         <v>11</v>
@@ -7449,10 +7375,10 @@
         <v>Crate 기믹 블록타입 | Corner_2x3_R</v>
       </c>
       <c r="H127" s="9" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
       <c r="I127" s="9" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="J127" s="9"/>
     </row>
@@ -7462,10 +7388,10 @@
         <v>CrateBlock_Type|12</v>
       </c>
       <c r="C128" s="9" t="s">
-        <v>423</v>
+        <v>408</v>
       </c>
       <c r="D128" s="9" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="E128" s="9">
         <v>12</v>
@@ -7475,10 +7401,10 @@
         <v>Crate 기믹 블록타입 | Corner_2x4</v>
       </c>
       <c r="H128" s="9" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
       <c r="I128" s="9" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="J128" s="9"/>
     </row>
@@ -7488,10 +7414,10 @@
         <v>CrateBlock_Type|13</v>
       </c>
       <c r="C129" s="9" t="s">
-        <v>423</v>
+        <v>408</v>
       </c>
       <c r="D129" s="9" t="s">
-        <v>432</v>
+        <v>417</v>
       </c>
       <c r="E129" s="9">
         <v>13</v>
@@ -7501,10 +7427,10 @@
         <v>Crate 기믹 블록타입 | Corner_2x4_R</v>
       </c>
       <c r="H129" s="9" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
       <c r="I129" s="9" t="s">
-        <v>432</v>
+        <v>417</v>
       </c>
       <c r="J129" s="9"/>
     </row>
@@ -7514,10 +7440,10 @@
         <v>CrateBlock_Type|14</v>
       </c>
       <c r="C130" s="9" t="s">
-        <v>423</v>
+        <v>408</v>
       </c>
       <c r="D130" s="9" t="s">
-        <v>441</v>
+        <v>426</v>
       </c>
       <c r="E130" s="9">
         <v>14</v>
@@ -7527,10 +7453,10 @@
         <v>Crate 기믹 블록타입 | Corner_3x4</v>
       </c>
       <c r="H130" s="9" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
       <c r="I130" s="9" t="s">
-        <v>441</v>
+        <v>426</v>
       </c>
       <c r="J130" s="9"/>
     </row>
@@ -7540,10 +7466,10 @@
         <v>CrateBlock_Type|15</v>
       </c>
       <c r="C131" s="9" t="s">
-        <v>423</v>
+        <v>408</v>
       </c>
       <c r="D131" s="9" t="s">
-        <v>440</v>
+        <v>425</v>
       </c>
       <c r="E131" s="9">
         <v>15</v>
@@ -7553,10 +7479,10 @@
         <v>Crate 기믹 블록타입 | Corner_3x4_R</v>
       </c>
       <c r="H131" s="9" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
       <c r="I131" s="9" t="s">
-        <v>440</v>
+        <v>425</v>
       </c>
       <c r="J131" s="9"/>
     </row>
@@ -7566,10 +7492,10 @@
         <v>CrateBlock_Type|16</v>
       </c>
       <c r="C132" s="9" t="s">
-        <v>423</v>
+        <v>408</v>
       </c>
       <c r="D132" s="9" t="s">
-        <v>433</v>
+        <v>418</v>
       </c>
       <c r="E132" s="9">
         <v>16</v>
@@ -7579,10 +7505,10 @@
         <v>Crate 기믹 블록타입 | T_3x2</v>
       </c>
       <c r="H132" s="9" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
       <c r="I132" s="9" t="s">
-        <v>433</v>
+        <v>418</v>
       </c>
       <c r="J132" s="9"/>
     </row>
@@ -7592,10 +7518,10 @@
         <v>CrateBlock_Type|17</v>
       </c>
       <c r="C133" s="9" t="s">
-        <v>423</v>
+        <v>408</v>
       </c>
       <c r="D133" s="9" t="s">
-        <v>434</v>
+        <v>419</v>
       </c>
       <c r="E133" s="9">
         <v>17</v>
@@ -7605,10 +7531,10 @@
         <v>Crate 기믹 블록타입 | T_3x3</v>
       </c>
       <c r="H133" s="9" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
       <c r="I133" s="9" t="s">
-        <v>434</v>
+        <v>419</v>
       </c>
       <c r="J133" s="9"/>
     </row>
@@ -7618,7 +7544,7 @@
         <v>CrateBlock_Type|18</v>
       </c>
       <c r="C134" s="9" t="s">
-        <v>423</v>
+        <v>408</v>
       </c>
       <c r="D134" s="9" t="s">
         <v>185</v>
@@ -7631,7 +7557,7 @@
         <v>Crate 기믹 블록타입 | Cross_3x3</v>
       </c>
       <c r="H134" s="9" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
       <c r="I134" s="9" t="s">
         <v>185</v>
@@ -7644,10 +7570,10 @@
         <v>CrateBlock_Type|19</v>
       </c>
       <c r="C135" s="9" t="s">
-        <v>423</v>
+        <v>408</v>
       </c>
       <c r="D135" s="9" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="E135" s="9">
         <v>19</v>
@@ -7657,10 +7583,10 @@
         <v>Crate 기믹 블록타입 | Cross_5x5</v>
       </c>
       <c r="H135" s="9" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
       <c r="I135" s="9" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="J135" s="9"/>
     </row>
@@ -7670,10 +7596,10 @@
         <v>CrateBlock_Type|20</v>
       </c>
       <c r="C136" s="9" t="s">
-        <v>423</v>
+        <v>408</v>
       </c>
       <c r="D136" s="9" t="s">
-        <v>443</v>
+        <v>428</v>
       </c>
       <c r="E136" s="9">
         <v>20</v>
@@ -7683,10 +7609,10 @@
         <v>Crate 기믹 블록타입 | S_3x2</v>
       </c>
       <c r="H136" s="9" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
       <c r="I136" s="9" t="s">
-        <v>443</v>
+        <v>428</v>
       </c>
       <c r="J136" s="9"/>
     </row>
@@ -7696,10 +7622,10 @@
         <v>CrateBlock_Type|21</v>
       </c>
       <c r="C137" s="9" t="s">
-        <v>423</v>
+        <v>408</v>
       </c>
       <c r="D137" s="9" t="s">
-        <v>444</v>
+        <v>429</v>
       </c>
       <c r="E137" s="9">
         <v>21</v>
@@ -7709,10 +7635,10 @@
         <v>Crate 기믹 블록타입 | Z_3x2</v>
       </c>
       <c r="H137" s="9" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
       <c r="I137" s="9" t="s">
-        <v>444</v>
+        <v>429</v>
       </c>
       <c r="J137" s="9"/>
     </row>
@@ -8816,7 +8742,7 @@
         <v>67</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>490</v>
+        <v>467</v>
       </c>
       <c r="J12" s="9"/>
     </row>
@@ -8842,7 +8768,7 @@
         <v>160</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>491</v>
+        <v>468</v>
       </c>
       <c r="J13" s="9"/>
     </row>
@@ -8907,7 +8833,7 @@
         <v>158</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="E16" s="9">
         <v>8</v>
@@ -8920,7 +8846,7 @@
         <v>160</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="J16" s="9"/>
     </row>
@@ -8933,7 +8859,7 @@
         <v>65</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>486</v>
+        <v>463</v>
       </c>
       <c r="E17" s="9">
         <v>9</v>
@@ -8946,7 +8872,7 @@
         <v>67</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>488</v>
+        <v>465</v>
       </c>
       <c r="J17" s="9"/>
     </row>
@@ -8959,7 +8885,7 @@
         <v>65</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>487</v>
+        <v>464</v>
       </c>
       <c r="E18" s="9">
         <v>10</v>
@@ -8972,7 +8898,7 @@
         <v>67</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>489</v>
+        <v>466</v>
       </c>
       <c r="J18" s="9"/>
     </row>
@@ -8985,7 +8911,7 @@
         <v>65</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>528</v>
+        <v>505</v>
       </c>
       <c r="E19" s="9">
         <v>11</v>
@@ -8998,7 +8924,7 @@
         <v>67</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>529</v>
+        <v>506</v>
       </c>
       <c r="J19" s="9"/>
     </row>
@@ -9011,7 +8937,7 @@
         <v>65</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>536</v>
+        <v>513</v>
       </c>
       <c r="E20" s="9">
         <v>12</v>
@@ -9024,7 +8950,7 @@
         <v>67</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>538</v>
+        <v>515</v>
       </c>
       <c r="J20" s="9"/>
     </row>
@@ -9037,7 +8963,7 @@
         <v>65</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>537</v>
+        <v>514</v>
       </c>
       <c r="E21" s="9">
         <v>13</v>
@@ -9050,7 +8976,7 @@
         <v>67</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>539</v>
+        <v>516</v>
       </c>
       <c r="J21" s="9"/>
     </row>
@@ -9167,7 +9093,7 @@
         <v>86</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="E26" s="9">
         <v>4</v>
@@ -9180,7 +9106,7 @@
         <v>87</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="J26" s="9"/>
     </row>
@@ -9242,10 +9168,10 @@
         <v>ADS_GROUP_TYPE|0</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>353</v>
+        <v>343</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="E29" s="9">
         <v>0</v>
@@ -9255,10 +9181,10 @@
         <v>광고 그룹 타입 | None</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="J29" s="9"/>
     </row>
@@ -9268,10 +9194,10 @@
         <v>ADS_GROUP_TYPE|1</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>353</v>
+        <v>343</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>480</v>
+        <v>457</v>
       </c>
       <c r="E30" s="9">
         <v>1</v>
@@ -9281,10 +9207,10 @@
         <v>광고 그룹 타입 | 스테이지 클리어 OR 플레이시간 Segment 1</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>484</v>
+        <v>461</v>
       </c>
       <c r="J30" s="9"/>
     </row>
@@ -9294,10 +9220,10 @@
         <v>ADS_GROUP_TYPE|2</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>353</v>
+        <v>343</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="E31" s="9">
         <v>2</v>
@@ -9307,10 +9233,10 @@
         <v>광고 그룹 타입 | 스테이지 클리어 AND 플레이 시간 Segment 1</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>485</v>
+        <v>462</v>
       </c>
       <c r="J31" s="9"/>
     </row>
@@ -9320,10 +9246,10 @@
         <v>ADS_GROUP_TYPE|3</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>353</v>
+        <v>343</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>481</v>
+        <v>458</v>
       </c>
       <c r="E32" s="9">
         <v>3</v>
@@ -9333,10 +9259,10 @@
         <v>광고 그룹 타입 | 스테이지 클리어 OR 플레이시간 Segment 2</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>482</v>
+        <v>459</v>
       </c>
       <c r="J32" s="9"/>
     </row>
@@ -9346,10 +9272,10 @@
         <v>ADS_GROUP_TYPE|4</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>353</v>
+        <v>343</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>479</v>
+        <v>456</v>
       </c>
       <c r="E33" s="9">
         <v>4</v>
@@ -9359,10 +9285,10 @@
         <v>광고 그룹 타입 | 스테이지 클리어 AND 플레이 시간 Segment 2</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="I33" s="9" t="s">
-        <v>483</v>
+        <v>460</v>
       </c>
       <c r="J33" s="9"/>
     </row>
@@ -9372,10 +9298,10 @@
         <v>ADS_GROUP_TYPE|5</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>353</v>
+        <v>343</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>540</v>
+        <v>517</v>
       </c>
       <c r="E34" s="9">
         <v>5</v>
@@ -9385,10 +9311,10 @@
         <v>광고 그룹 타입 | 스테이지 클리어 OR 플레이시간 Segment 3</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>541</v>
+        <v>518</v>
       </c>
       <c r="J34" s="9"/>
     </row>
@@ -9398,7 +9324,7 @@
         <v>ADS_SEGMENT_TYPE|0</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>530</v>
+        <v>507</v>
       </c>
       <c r="D35" s="9" t="s">
         <v>41</v>
@@ -9411,7 +9337,7 @@
         <v>광고 세그먼트 타입 | None</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>533</v>
+        <v>510</v>
       </c>
       <c r="I35" s="9" t="s">
         <v>41</v>
@@ -9424,10 +9350,10 @@
         <v>ADS_SEGMENT_TYPE|1</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>530</v>
+        <v>507</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>531</v>
+        <v>508</v>
       </c>
       <c r="E36" s="9">
         <v>1</v>
@@ -9437,10 +9363,10 @@
         <v>광고 세그먼트 타입 | 로컬 조건 체크</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>533</v>
+        <v>510</v>
       </c>
       <c r="I36" s="9" t="s">
-        <v>534</v>
+        <v>511</v>
       </c>
       <c r="J36" s="9"/>
     </row>
@@ -9450,10 +9376,10 @@
         <v>ADS_SEGMENT_TYPE|2</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>530</v>
+        <v>507</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>532</v>
+        <v>509</v>
       </c>
       <c r="E37" s="9">
         <v>2</v>
@@ -9463,10 +9389,10 @@
         <v>광고 세그먼트 타입 | AB 테스트</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>533</v>
+        <v>510</v>
       </c>
       <c r="I37" s="9" t="s">
-        <v>535</v>
+        <v>512</v>
       </c>
       <c r="J37" s="9"/>
     </row>
@@ -10669,7 +10595,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4CAC25C-A637-9C4F-99F2-EEE59B30A5B9}">
-  <dimension ref="A2:J86"/>
+  <dimension ref="A2:J71"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.25"/>
   <cols>
     <col min="1" max="1" width="6.6640625" style="2" bestFit="1" customWidth="1"/>
@@ -10768,11 +10694,11 @@
     </row>
     <row r="5" spans="1:10">
       <c r="B5" s="8" t="str">
-        <f t="shared" ref="B5:B12" si="0">C5&amp;"|"&amp;E5</f>
+        <f t="shared" ref="B5:B11" si="0">C5&amp;"|"&amp;E5</f>
         <v>Item_Type|0</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="D5" s="9" t="s">
         <v>41</v>
@@ -10780,9 +10706,9 @@
       <c r="E5" s="9">
         <v>0</v>
       </c>
-      <c r="F5" s="8" t="e">
-        <f>IF(H5="", "", H5&amp;IF(I5="", "", " | "&amp;I5)&amp;IF(#REF!="", "", " | "&amp;#REF!))</f>
-        <v>#REF!</v>
+      <c r="F5" s="8" t="str">
+        <f>IF(H5="", "", H5&amp;IF(I5="", "", " | "&amp;I5)&amp;IF(J8="", "", " | "&amp;J8))</f>
+        <v>아이템 타입 | None</v>
       </c>
       <c r="H5" s="9" t="s">
         <v>55</v>
@@ -10798,7 +10724,7 @@
         <v>Item_Type|101</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="D6" s="9" t="s">
         <v>63</v>
@@ -10807,7 +10733,7 @@
         <v>101</v>
       </c>
       <c r="F6" s="8" t="str">
-        <f t="shared" ref="F6:F9" si="1">IF(H6="", "", H6&amp;IF(I6="", "", " | "&amp;I6)&amp;IF(J13="", "", " | "&amp;J13))</f>
+        <f>IF(H6="", "", H6&amp;IF(I6="", "", " | "&amp;I6)&amp;IF(J12="", "", " | "&amp;J12))</f>
         <v>아이템 타입 | Coin</v>
       </c>
       <c r="H6" s="9" t="s">
@@ -10824,7 +10750,7 @@
         <v>Item_Type|102</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>42</v>
@@ -10833,7 +10759,7 @@
         <v>102</v>
       </c>
       <c r="F7" s="8" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(H7="", "", H7&amp;IF(I7="", "", " | "&amp;I7)&amp;IF(J13="", "", " | "&amp;J13))</f>
         <v>아이템 타입 | Heart</v>
       </c>
       <c r="H7" s="9" t="s">
@@ -10850,23 +10776,23 @@
         <v>Item_Type|201</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>231</v>
+        <v>523</v>
       </c>
       <c r="E8" s="9">
         <v>201</v>
       </c>
       <c r="F8" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>아이템 타입 | FreezeTimer</v>
+        <f>IF(H8="", "", H8&amp;IF(I8="", "", " | "&amp;I8)&amp;IF(J14="", "", " | "&amp;J14))</f>
+        <v>아이템 타입 | Undo</v>
       </c>
       <c r="H8" s="9" t="s">
         <v>55</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>231</v>
+        <v>523</v>
       </c>
       <c r="J8" s="9"/>
     </row>
@@ -10876,23 +10802,23 @@
         <v>Item_Type|202</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>232</v>
+        <v>524</v>
       </c>
       <c r="E9" s="9">
         <v>202</v>
       </c>
       <c r="F9" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>아이템 타입 | Hammer</v>
+        <f>IF(H9="", "", H9&amp;IF(I9="", "", " | "&amp;I9)&amp;IF(J15="", "", " | "&amp;J15))</f>
+        <v>아이템 타입 | Hint</v>
       </c>
       <c r="H9" s="9" t="s">
         <v>55</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>232</v>
+        <v>524</v>
       </c>
       <c r="J9" s="9"/>
     </row>
@@ -10902,23 +10828,23 @@
         <v>Item_Type|203</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>233</v>
+        <v>525</v>
       </c>
       <c r="E10" s="9">
         <v>203</v>
       </c>
       <c r="F10" s="8" t="str">
-        <f>IF(H10="", "", H10&amp;IF(I10="", "", " | "&amp;I10)&amp;IF(J28="", "", " | "&amp;J28))</f>
-        <v>아이템 타입 | ColorVacuum</v>
+        <f>IF(H10="", "", H10&amp;IF(I10="", "", " | "&amp;I10)&amp;IF(J16="", "", " | "&amp;J16))</f>
+        <v>아이템 타입 | TripleArrow</v>
       </c>
       <c r="H10" s="9" t="s">
         <v>55</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>233</v>
+        <v>525</v>
       </c>
       <c r="J10" s="9"/>
     </row>
@@ -10928,700 +10854,460 @@
         <v>Item_Type|204</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>234</v>
+        <v>526</v>
       </c>
       <c r="E11" s="9">
         <v>204</v>
       </c>
       <c r="F11" s="8" t="str">
-        <f>IF(H11="", "", H11&amp;IF(I11="", "", " | "&amp;I11)&amp;IF(J29="", "", " | "&amp;J29))</f>
-        <v>아이템 타입 | Rocket</v>
+        <f>IF(H11="", "", H11&amp;IF(I11="", "", " | "&amp;I11)&amp;IF(J17="", "", " | "&amp;J17))</f>
+        <v>아이템 타입 | DartArrow</v>
       </c>
       <c r="H11" s="9" t="s">
         <v>55</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>234</v>
+        <v>526</v>
       </c>
       <c r="J11" s="9"/>
     </row>
     <row r="12" spans="1:10">
       <c r="B12" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>Item_Type|301</v>
+        <f t="shared" ref="B12" si="1">C12&amp;"|"&amp;E12</f>
+        <v>Item_Type|404</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>248</v>
+        <v>232</v>
       </c>
       <c r="E12" s="9">
-        <v>301</v>
+        <v>404</v>
       </c>
       <c r="F12" s="8" t="str">
-        <f>IF(H12="", "", H12&amp;IF(I12="", "", " | "&amp;I12)&amp;IF(J30="", "", " | "&amp;J30))</f>
-        <v>아이템 타입 | InfiniteHeart</v>
+        <f>IF(H12="", "", H12&amp;IF(I12="", "", " | "&amp;I12)&amp;IF(J20="", "", " | "&amp;J20))</f>
+        <v>아이템 타입 | NoAds</v>
       </c>
       <c r="H12" s="9" t="s">
         <v>55</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>248</v>
+        <v>231</v>
       </c>
       <c r="J12" s="9"/>
     </row>
     <row r="13" spans="1:10">
       <c r="B13" s="8" t="str">
-        <f t="shared" ref="B13:B14" si="2">C13&amp;"|"&amp;E13</f>
-        <v>Item_Type|404</v>
+        <f t="shared" ref="B13" si="2">C13&amp;"|"&amp;E13</f>
+        <v>Item_GetType|0</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="E13" s="9">
-        <v>404</v>
+        <v>0</v>
       </c>
       <c r="F13" s="8" t="str">
-        <f t="shared" ref="F13:F23" si="3">IF(H13="", "", H13&amp;IF(I13="", "", " | "&amp;I13)&amp;IF(J35="", "", " | "&amp;J35))</f>
-        <v>아이템 타입 | NoAds</v>
+        <f t="shared" ref="F13:F21" si="3">IF(H13="", "", H13&amp;IF(I13="", "", " | "&amp;I13)&amp;IF(J24="", "", " | "&amp;J24))</f>
+        <v>아이템 획득 방법 | None</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>55</v>
+        <v>253</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>235</v>
+        <v>252</v>
       </c>
       <c r="J13" s="9"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v>Item_Type|501</v>
+        <f t="shared" ref="B14" si="4">C14&amp;"|"&amp;E14</f>
+        <v>Item_GetType|1</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>237</v>
+        <v>254</v>
       </c>
       <c r="E14" s="9">
-        <v>501</v>
+        <v>1</v>
       </c>
       <c r="F14" s="8" t="str">
         <f t="shared" si="3"/>
-        <v>아이템 타입 | AdditionalTime</v>
+        <v>아이템 획득 방법 | Default(초기 사용자 계정에 지급된 상태)</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>55</v>
+        <v>253</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>237</v>
+        <v>257</v>
       </c>
       <c r="J14" s="9"/>
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="8" t="str">
-        <f t="shared" ref="B15:B28" si="4">C15&amp;"|"&amp;E15</f>
-        <v>Item_Type|502</v>
+        <f t="shared" ref="B15" si="5">C15&amp;"|"&amp;E15</f>
+        <v>Item_GetType|2</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>239</v>
+        <v>255</v>
       </c>
       <c r="E15" s="9">
-        <v>502</v>
+        <v>2</v>
       </c>
       <c r="F15" s="8" t="str">
         <f t="shared" si="3"/>
-        <v>아이템 타입 | ReverseGate</v>
+        <v>아이템 획득 방법 | Price(Item_Price 지급)</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>55</v>
+        <v>253</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>238</v>
+        <v>258</v>
       </c>
       <c r="J15" s="9"/>
     </row>
     <row r="16" spans="1:10">
       <c r="B16" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>Item_Type|503</v>
+        <f t="shared" ref="B16:B21" si="6">C16&amp;"|"&amp;E16</f>
+        <v>Item_GetType|3</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>241</v>
+        <v>256</v>
       </c>
       <c r="E16" s="9">
-        <v>503</v>
+        <v>3</v>
       </c>
       <c r="F16" s="8" t="str">
         <f t="shared" si="3"/>
-        <v>아이템 타입 | AdditionalBombTime</v>
+        <v>아이템 획득 방법 | AdsFree</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>55</v>
+        <v>253</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>240</v>
+        <v>256</v>
       </c>
       <c r="J16" s="9"/>
     </row>
     <row r="17" spans="2:10">
       <c r="B17" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>Item_Type|504</v>
+        <f t="shared" si="6"/>
+        <v>Item_Category|0</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>402</v>
+        <v>252</v>
       </c>
       <c r="E17" s="9">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="F17" s="8" t="str">
         <f t="shared" si="3"/>
-        <v>아이템 타입 | DoorLockMove</v>
+        <v>아이템 카테고리 | None</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>55</v>
+        <v>264</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>402</v>
+        <v>252</v>
       </c>
       <c r="J17" s="9"/>
     </row>
     <row r="18" spans="2:10">
       <c r="B18" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>Item_Type|505</v>
+        <f t="shared" si="6"/>
+        <v>Item_Category|1</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>466</v>
+        <v>260</v>
       </c>
       <c r="E18" s="9">
-        <v>505</v>
+        <v>1</v>
       </c>
       <c r="F18" s="8" t="str">
         <f t="shared" si="3"/>
-        <v>아이템 타입 | ChangeGateColor</v>
+        <v>아이템 카테고리 | 재화</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>55</v>
+        <v>264</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>466</v>
+        <v>265</v>
       </c>
       <c r="J18" s="9"/>
     </row>
-    <row r="19" spans="2:10">
+    <row r="19" spans="2:10" ht="10.5" customHeight="1">
       <c r="B19" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>Item_Type|506</v>
+        <f t="shared" si="6"/>
+        <v>Item_Category|2</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>467</v>
+        <v>261</v>
       </c>
       <c r="E19" s="9">
-        <v>506</v>
+        <v>2</v>
       </c>
       <c r="F19" s="8" t="str">
         <f t="shared" si="3"/>
-        <v>아이템 타입 | ChangeGateSize</v>
+        <v>아이템 카테고리 | 소비성 아이템</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>55</v>
+        <v>264</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>467</v>
+        <v>266</v>
       </c>
       <c r="J19" s="9"/>
     </row>
-    <row r="20" spans="2:10">
+    <row r="20" spans="2:10" ht="10.5" customHeight="1">
       <c r="B20" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>Item_Type|507</v>
+        <f t="shared" si="6"/>
+        <v>Item_Category|3</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>468</v>
+        <v>262</v>
       </c>
       <c r="E20" s="9">
-        <v>507</v>
+        <v>3</v>
       </c>
       <c r="F20" s="8" t="str">
         <f t="shared" si="3"/>
-        <v>아이템 타입 | AddDynamiteCount</v>
+        <v>아이템 카테고리 | 버프</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>55</v>
+        <v>264</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>468</v>
+        <v>267</v>
       </c>
       <c r="J20" s="9"/>
     </row>
-    <row r="21" spans="2:10">
+    <row r="21" spans="2:10" ht="10.5" customHeight="1">
       <c r="B21" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>Item_Type|508</v>
+        <f t="shared" si="6"/>
+        <v>Item_Category|4</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>469</v>
+        <v>263</v>
       </c>
       <c r="E21" s="9">
-        <v>508</v>
+        <v>4</v>
       </c>
       <c r="F21" s="8" t="str">
         <f t="shared" si="3"/>
-        <v>아이템 타입 | ReverseCurtain</v>
+        <v>아이템 카테고리 | 이어 하기 아이템</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>55</v>
+        <v>264</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>469</v>
+        <v>268</v>
       </c>
       <c r="J21" s="9"/>
     </row>
-    <row r="22" spans="2:10">
+    <row r="22" spans="2:10" ht="10.5" customHeight="1">
       <c r="B22" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>Item_Type|509</v>
+        <f t="shared" ref="B22" si="7">C22&amp;"|"&amp;E22</f>
+        <v>Item_Category|5</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>470</v>
+        <v>402</v>
       </c>
       <c r="E22" s="9">
-        <v>509</v>
+        <v>5</v>
       </c>
       <c r="F22" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v>아이템 타입 | SwitchGateColor</v>
+        <f t="shared" ref="F22" si="8">IF(H22="", "", H22&amp;IF(I22="", "", " | "&amp;I22)&amp;IF(J33="", "", " | "&amp;J33))</f>
+        <v>아이템 카테고리 | 스타팅 부스터</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>55</v>
+        <v>264</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>470</v>
+        <v>403</v>
       </c>
       <c r="J22" s="9"/>
     </row>
-    <row r="23" spans="2:10">
-      <c r="B23" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>Item_Type|510</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>249</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>471</v>
-      </c>
-      <c r="E23" s="9">
-        <v>510</v>
-      </c>
-      <c r="F23" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v>아이템 타입 | JumpingSingleDoorMove</v>
-      </c>
-      <c r="H23" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="I23" s="9" t="s">
-        <v>471</v>
-      </c>
+    <row r="23" spans="2:10" ht="10.5" customHeight="1">
+      <c r="B23" s="8"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="8"/>
+      <c r="H23" s="9"/>
+      <c r="I23" s="9"/>
       <c r="J23" s="9"/>
     </row>
-    <row r="24" spans="2:10">
-      <c r="B24" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>Item_Type|601</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>249</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>415</v>
-      </c>
-      <c r="E24" s="9">
-        <v>601</v>
-      </c>
-      <c r="F24" s="8" t="str">
-        <f>IF(H24="", "", H24&amp;IF(I24="", "", " | "&amp;I24)&amp;IF(J40="", "", " | "&amp;J40))</f>
-        <v>아이템 타입 | AddTimer 부스터</v>
-      </c>
-      <c r="H24" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="I24" s="9" t="s">
-        <v>416</v>
-      </c>
+    <row r="24" spans="2:10" ht="10.5" customHeight="1">
+      <c r="B24" s="8"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="8"/>
+      <c r="H24" s="9"/>
+      <c r="I24" s="9"/>
       <c r="J24" s="9"/>
     </row>
-    <row r="25" spans="2:10">
-      <c r="B25" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>Item_Type|602</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>249</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>417</v>
-      </c>
-      <c r="E25" s="9">
-        <v>602</v>
-      </c>
-      <c r="F25" s="8" t="str">
-        <f>IF(H25="", "", H25&amp;IF(I25="", "", " | "&amp;I25)&amp;IF(J41="", "", " | "&amp;J41))</f>
-        <v>아이템 타입 | RandomRocket 부스터</v>
-      </c>
-      <c r="H25" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="I25" s="9" t="s">
-        <v>418</v>
-      </c>
+    <row r="25" spans="2:10" ht="10.5" customHeight="1">
+      <c r="B25" s="8"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="8"/>
+      <c r="H25" s="9"/>
+      <c r="I25" s="9"/>
       <c r="J25" s="9"/>
     </row>
-    <row r="26" spans="2:10">
-      <c r="B26" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>Item_Type|603</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>249</v>
-      </c>
-      <c r="D26" s="9" t="s">
-        <v>473</v>
-      </c>
-      <c r="E26" s="9">
-        <v>603</v>
-      </c>
-      <c r="F26" s="8" t="str">
-        <f t="shared" ref="F26:F27" si="5">IF(H26="", "", H26&amp;IF(I26="", "", " | "&amp;I26)&amp;IF(J42="", "", " | "&amp;J42))</f>
-        <v>아이템 타입 | InfiniteAddTimer</v>
-      </c>
-      <c r="H26" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="I26" s="9" t="s">
-        <v>473</v>
-      </c>
+    <row r="26" spans="2:10" ht="10.5" customHeight="1">
+      <c r="B26" s="8"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="8"/>
+      <c r="H26" s="9"/>
+      <c r="I26" s="9"/>
       <c r="J26" s="9"/>
     </row>
-    <row r="27" spans="2:10">
-      <c r="B27" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>Item_Type|604</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>249</v>
-      </c>
-      <c r="D27" s="9" t="s">
-        <v>474</v>
-      </c>
-      <c r="E27" s="9">
-        <v>604</v>
-      </c>
-      <c r="F27" s="8" t="str">
-        <f t="shared" si="5"/>
-        <v>아이템 타입 | InfiniteRandomRocket</v>
-      </c>
-      <c r="H27" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="I27" s="9" t="s">
-        <v>474</v>
-      </c>
+    <row r="27" spans="2:10" ht="10.5" customHeight="1">
+      <c r="B27" s="8"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="8"/>
+      <c r="H27" s="9"/>
+      <c r="I27" s="9"/>
       <c r="J27" s="9"/>
     </row>
-    <row r="28" spans="2:10">
-      <c r="B28" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>Item_GetType|0</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="D28" s="9" t="s">
-        <v>262</v>
-      </c>
-      <c r="E28" s="9">
-        <v>0</v>
-      </c>
-      <c r="F28" s="8" t="str">
-        <f t="shared" ref="F28:F36" si="6">IF(H28="", "", H28&amp;IF(I28="", "", " | "&amp;I28)&amp;IF(J39="", "", " | "&amp;J39))</f>
-        <v>아이템 획득 방법 | None</v>
-      </c>
-      <c r="H28" s="9" t="s">
-        <v>263</v>
-      </c>
-      <c r="I28" s="9" t="s">
-        <v>262</v>
-      </c>
+    <row r="28" spans="2:10" ht="10.5" customHeight="1">
+      <c r="B28" s="8"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="8"/>
+      <c r="H28" s="9"/>
+      <c r="I28" s="9"/>
       <c r="J28" s="9"/>
     </row>
-    <row r="29" spans="2:10">
-      <c r="B29" s="8" t="str">
-        <f t="shared" ref="B29" si="7">C29&amp;"|"&amp;E29</f>
-        <v>Item_GetType|1</v>
-      </c>
-      <c r="C29" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="D29" s="9" t="s">
-        <v>264</v>
-      </c>
-      <c r="E29" s="9">
-        <v>1</v>
-      </c>
-      <c r="F29" s="8" t="str">
-        <f t="shared" si="6"/>
-        <v>아이템 획득 방법 | Default(초기 사용자 계정에 지급된 상태)</v>
-      </c>
-      <c r="H29" s="9" t="s">
-        <v>263</v>
-      </c>
-      <c r="I29" s="9" t="s">
-        <v>267</v>
-      </c>
+    <row r="29" spans="2:10" ht="10.5" customHeight="1">
+      <c r="B29" s="8"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="8"/>
+      <c r="H29" s="9"/>
+      <c r="I29" s="9"/>
       <c r="J29" s="9"/>
     </row>
-    <row r="30" spans="2:10">
-      <c r="B30" s="8" t="str">
-        <f t="shared" ref="B30" si="8">C30&amp;"|"&amp;E30</f>
-        <v>Item_GetType|2</v>
-      </c>
-      <c r="C30" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="D30" s="9" t="s">
-        <v>265</v>
-      </c>
-      <c r="E30" s="9">
-        <v>2</v>
-      </c>
-      <c r="F30" s="8" t="str">
-        <f t="shared" si="6"/>
-        <v>아이템 획득 방법 | Price(Item_Price 지급)</v>
-      </c>
-      <c r="H30" s="9" t="s">
-        <v>263</v>
-      </c>
-      <c r="I30" s="9" t="s">
-        <v>268</v>
-      </c>
+    <row r="30" spans="2:10" ht="10.5" customHeight="1">
+      <c r="B30" s="8"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="8"/>
+      <c r="H30" s="9"/>
+      <c r="I30" s="9"/>
       <c r="J30" s="9"/>
     </row>
-    <row r="31" spans="2:10">
-      <c r="B31" s="8" t="str">
-        <f t="shared" ref="B31:B36" si="9">C31&amp;"|"&amp;E31</f>
-        <v>Item_GetType|3</v>
-      </c>
-      <c r="C31" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="D31" s="9" t="s">
-        <v>266</v>
-      </c>
-      <c r="E31" s="9">
-        <v>3</v>
-      </c>
-      <c r="F31" s="8" t="str">
-        <f t="shared" si="6"/>
-        <v>아이템 획득 방법 | AdsFree</v>
-      </c>
-      <c r="H31" s="9" t="s">
-        <v>263</v>
-      </c>
-      <c r="I31" s="9" t="s">
-        <v>266</v>
-      </c>
+    <row r="31" spans="2:10" ht="10.5" customHeight="1">
+      <c r="B31" s="8"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="8"/>
+      <c r="H31" s="9"/>
+      <c r="I31" s="9"/>
       <c r="J31" s="9"/>
     </row>
-    <row r="32" spans="2:10">
-      <c r="B32" s="8" t="str">
-        <f t="shared" si="9"/>
-        <v>Item_Category|0</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>269</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>262</v>
-      </c>
-      <c r="E32" s="9">
-        <v>0</v>
-      </c>
-      <c r="F32" s="8" t="str">
-        <f t="shared" si="6"/>
-        <v>아이템 카테고리 | None</v>
-      </c>
-      <c r="H32" s="9" t="s">
-        <v>274</v>
-      </c>
-      <c r="I32" s="9" t="s">
-        <v>262</v>
-      </c>
+    <row r="32" spans="2:10" ht="10.5" customHeight="1">
+      <c r="B32" s="8"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="8"/>
+      <c r="H32" s="9"/>
+      <c r="I32" s="9"/>
       <c r="J32" s="9"/>
     </row>
-    <row r="33" spans="2:10">
-      <c r="B33" s="8" t="str">
-        <f t="shared" si="9"/>
-        <v>Item_Category|1</v>
-      </c>
-      <c r="C33" s="9" t="s">
-        <v>269</v>
-      </c>
-      <c r="D33" s="9" t="s">
-        <v>270</v>
-      </c>
-      <c r="E33" s="9">
-        <v>1</v>
-      </c>
-      <c r="F33" s="8" t="str">
-        <f t="shared" si="6"/>
-        <v>아이템 카테고리 | 재화</v>
-      </c>
-      <c r="H33" s="9" t="s">
-        <v>274</v>
-      </c>
-      <c r="I33" s="9" t="s">
-        <v>275</v>
-      </c>
+    <row r="33" spans="2:10" ht="10.5" customHeight="1">
+      <c r="B33" s="8"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="8"/>
+      <c r="H33" s="9"/>
+      <c r="I33" s="9"/>
       <c r="J33" s="9"/>
     </row>
     <row r="34" spans="2:10" ht="10.5" customHeight="1">
-      <c r="B34" s="8" t="str">
-        <f t="shared" si="9"/>
-        <v>Item_Category|2</v>
-      </c>
-      <c r="C34" s="9" t="s">
-        <v>269</v>
-      </c>
-      <c r="D34" s="9" t="s">
-        <v>271</v>
-      </c>
-      <c r="E34" s="9">
-        <v>2</v>
-      </c>
-      <c r="F34" s="8" t="str">
-        <f t="shared" si="6"/>
-        <v>아이템 카테고리 | 소비성 아이템</v>
-      </c>
-      <c r="H34" s="9" t="s">
-        <v>274</v>
-      </c>
-      <c r="I34" s="9" t="s">
-        <v>276</v>
-      </c>
+      <c r="B34" s="8"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="8"/>
+      <c r="H34" s="9"/>
+      <c r="I34" s="9"/>
       <c r="J34" s="9"/>
     </row>
     <row r="35" spans="2:10" ht="10.5" customHeight="1">
-      <c r="B35" s="8" t="str">
-        <f t="shared" si="9"/>
-        <v>Item_Category|3</v>
-      </c>
-      <c r="C35" s="9" t="s">
-        <v>269</v>
-      </c>
-      <c r="D35" s="9" t="s">
-        <v>272</v>
-      </c>
-      <c r="E35" s="9">
-        <v>3</v>
-      </c>
-      <c r="F35" s="8" t="str">
-        <f t="shared" si="6"/>
-        <v>아이템 카테고리 | 버프</v>
-      </c>
-      <c r="H35" s="9" t="s">
-        <v>274</v>
-      </c>
-      <c r="I35" s="9" t="s">
-        <v>277</v>
-      </c>
+      <c r="B35" s="8"/>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="9"/>
+      <c r="F35" s="8"/>
+      <c r="H35" s="9"/>
+      <c r="I35" s="9"/>
       <c r="J35" s="9"/>
     </row>
     <row r="36" spans="2:10" ht="10.5" customHeight="1">
-      <c r="B36" s="8" t="str">
-        <f t="shared" si="9"/>
-        <v>Item_Category|4</v>
-      </c>
-      <c r="C36" s="9" t="s">
-        <v>269</v>
-      </c>
-      <c r="D36" s="9" t="s">
-        <v>273</v>
-      </c>
-      <c r="E36" s="9">
-        <v>4</v>
-      </c>
-      <c r="F36" s="8" t="str">
-        <f t="shared" si="6"/>
-        <v>아이템 카테고리 | 이어 하기 아이템</v>
-      </c>
-      <c r="H36" s="9" t="s">
-        <v>274</v>
-      </c>
-      <c r="I36" s="9" t="s">
-        <v>278</v>
-      </c>
+      <c r="B36" s="8"/>
+      <c r="C36" s="9"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="9"/>
+      <c r="F36" s="8"/>
+      <c r="H36" s="9"/>
+      <c r="I36" s="9"/>
       <c r="J36" s="9"/>
     </row>
     <row r="37" spans="2:10" ht="10.5" customHeight="1">
-      <c r="B37" s="8" t="str">
-        <f t="shared" ref="B37" si="10">C37&amp;"|"&amp;E37</f>
-        <v>Item_Category|5</v>
-      </c>
-      <c r="C37" s="9" t="s">
-        <v>269</v>
-      </c>
-      <c r="D37" s="9" t="s">
-        <v>413</v>
-      </c>
-      <c r="E37" s="9">
-        <v>5</v>
-      </c>
-      <c r="F37" s="8" t="str">
-        <f t="shared" ref="F37" si="11">IF(H37="", "", H37&amp;IF(I37="", "", " | "&amp;I37)&amp;IF(J48="", "", " | "&amp;J48))</f>
-        <v>아이템 카테고리 | 스타팅 부스터</v>
-      </c>
-      <c r="H37" s="9" t="s">
-        <v>274</v>
-      </c>
-      <c r="I37" s="9" t="s">
-        <v>414</v>
-      </c>
+      <c r="B37" s="8"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="8"/>
+      <c r="H37" s="9"/>
+      <c r="I37" s="9"/>
       <c r="J37" s="9"/>
     </row>
     <row r="38" spans="2:10" ht="10.5" customHeight="1">
@@ -11725,113 +11411,36 @@
       <c r="J47" s="9"/>
     </row>
     <row r="48" spans="2:10" ht="10.5" customHeight="1">
-      <c r="B48" s="8"/>
-      <c r="C48" s="9"/>
-      <c r="D48" s="9"/>
-      <c r="E48" s="9"/>
-      <c r="F48" s="8"/>
-      <c r="H48" s="9"/>
-      <c r="I48" s="9"/>
       <c r="J48" s="9"/>
     </row>
     <row r="49" spans="2:10" ht="10.5" customHeight="1">
-      <c r="B49" s="8"/>
-      <c r="C49" s="9"/>
-      <c r="D49" s="9"/>
-      <c r="E49" s="9"/>
-      <c r="F49" s="8"/>
-      <c r="H49" s="9"/>
-      <c r="I49" s="9"/>
       <c r="J49" s="9"/>
     </row>
     <row r="50" spans="2:10" ht="10.5" customHeight="1">
-      <c r="B50" s="8"/>
-      <c r="C50" s="9"/>
-      <c r="D50" s="9"/>
-      <c r="E50" s="9"/>
-      <c r="F50" s="8"/>
-      <c r="H50" s="9"/>
-      <c r="I50" s="9"/>
       <c r="J50" s="9"/>
     </row>
     <row r="51" spans="2:10" ht="10.5" customHeight="1">
-      <c r="B51" s="8"/>
-      <c r="C51" s="9"/>
-      <c r="D51" s="9"/>
-      <c r="E51" s="9"/>
-      <c r="F51" s="8"/>
-      <c r="H51" s="9"/>
-      <c r="I51" s="9"/>
       <c r="J51" s="9"/>
     </row>
     <row r="52" spans="2:10" ht="10.5" customHeight="1">
-      <c r="B52" s="8"/>
-      <c r="C52" s="9"/>
-      <c r="D52" s="9"/>
-      <c r="E52" s="9"/>
-      <c r="F52" s="8"/>
-      <c r="H52" s="9"/>
-      <c r="I52" s="9"/>
       <c r="J52" s="9"/>
     </row>
     <row r="53" spans="2:10" ht="10.5" customHeight="1">
-      <c r="B53" s="8"/>
-      <c r="C53" s="9"/>
-      <c r="D53" s="9"/>
-      <c r="E53" s="9"/>
-      <c r="F53" s="8"/>
-      <c r="H53" s="9"/>
-      <c r="I53" s="9"/>
       <c r="J53" s="9"/>
     </row>
     <row r="54" spans="2:10" ht="10.5" customHeight="1">
-      <c r="B54" s="8"/>
-      <c r="C54" s="9"/>
-      <c r="D54" s="9"/>
-      <c r="E54" s="9"/>
-      <c r="F54" s="8"/>
-      <c r="H54" s="9"/>
-      <c r="I54" s="9"/>
       <c r="J54" s="9"/>
     </row>
     <row r="55" spans="2:10" ht="10.5" customHeight="1">
-      <c r="B55" s="8"/>
-      <c r="C55" s="9"/>
-      <c r="D55" s="9"/>
-      <c r="E55" s="9"/>
-      <c r="F55" s="8"/>
-      <c r="H55" s="9"/>
-      <c r="I55" s="9"/>
       <c r="J55" s="9"/>
     </row>
     <row r="56" spans="2:10" ht="10.5" customHeight="1">
-      <c r="B56" s="8"/>
-      <c r="C56" s="9"/>
-      <c r="D56" s="9"/>
-      <c r="E56" s="9"/>
-      <c r="F56" s="8"/>
-      <c r="H56" s="9"/>
-      <c r="I56" s="9"/>
       <c r="J56" s="9"/>
     </row>
     <row r="57" spans="2:10" ht="10.5" customHeight="1">
-      <c r="B57" s="8"/>
-      <c r="C57" s="9"/>
-      <c r="D57" s="9"/>
-      <c r="E57" s="9"/>
-      <c r="F57" s="8"/>
-      <c r="H57" s="9"/>
-      <c r="I57" s="9"/>
       <c r="J57" s="9"/>
     </row>
     <row r="58" spans="2:10" ht="10.5" customHeight="1">
-      <c r="B58" s="8"/>
-      <c r="C58" s="9"/>
-      <c r="D58" s="9"/>
-      <c r="E58" s="9"/>
-      <c r="F58" s="8"/>
-      <c r="H58" s="9"/>
-      <c r="I58" s="9"/>
       <c r="J58" s="9"/>
     </row>
     <row r="59" spans="2:10" ht="10.5" customHeight="1">
@@ -11855,23 +11464,9 @@
       <c r="J60" s="9"/>
     </row>
     <row r="61" spans="2:10" ht="10.5" customHeight="1">
-      <c r="B61" s="8"/>
-      <c r="C61" s="9"/>
-      <c r="D61" s="9"/>
-      <c r="E61" s="9"/>
-      <c r="F61" s="8"/>
-      <c r="H61" s="9"/>
-      <c r="I61" s="9"/>
       <c r="J61" s="9"/>
     </row>
     <row r="62" spans="2:10" ht="10.5" customHeight="1">
-      <c r="B62" s="8"/>
-      <c r="C62" s="9"/>
-      <c r="D62" s="9"/>
-      <c r="E62" s="9"/>
-      <c r="F62" s="8"/>
-      <c r="H62" s="9"/>
-      <c r="I62" s="9"/>
       <c r="J62" s="9"/>
     </row>
     <row r="63" spans="2:10" ht="10.5" customHeight="1">
@@ -11880,85 +11475,26 @@
     <row r="64" spans="2:10" ht="10.5" customHeight="1">
       <c r="J64" s="9"/>
     </row>
-    <row r="65" spans="2:10" ht="10.5" customHeight="1">
+    <row r="65" spans="10:10" ht="10.5" customHeight="1">
       <c r="J65" s="9"/>
     </row>
-    <row r="66" spans="2:10" ht="10.5" customHeight="1">
+    <row r="66" spans="10:10" ht="10.5" customHeight="1">
       <c r="J66" s="9"/>
     </row>
-    <row r="67" spans="2:10" ht="10.5" customHeight="1">
+    <row r="67" spans="10:10" ht="10.5" customHeight="1">
       <c r="J67" s="9"/>
     </row>
-    <row r="68" spans="2:10" ht="10.5" customHeight="1">
+    <row r="68" spans="10:10" ht="10.5" customHeight="1">
       <c r="J68" s="9"/>
     </row>
-    <row r="69" spans="2:10" ht="10.5" customHeight="1">
+    <row r="69" spans="10:10" ht="10.5" customHeight="1">
       <c r="J69" s="9"/>
     </row>
-    <row r="70" spans="2:10" ht="10.5" customHeight="1">
+    <row r="70" spans="10:10" ht="10.5" customHeight="1">
       <c r="J70" s="9"/>
     </row>
-    <row r="71" spans="2:10" ht="10.5" customHeight="1">
+    <row r="71" spans="10:10" ht="10.5" customHeight="1">
       <c r="J71" s="9"/>
-    </row>
-    <row r="72" spans="2:10" ht="10.5" customHeight="1">
-      <c r="J72" s="9"/>
-    </row>
-    <row r="73" spans="2:10" ht="10.5" customHeight="1">
-      <c r="J73" s="9"/>
-    </row>
-    <row r="74" spans="2:10" ht="10.5" customHeight="1">
-      <c r="B74" s="8"/>
-      <c r="C74" s="9"/>
-      <c r="D74" s="9"/>
-      <c r="E74" s="9"/>
-      <c r="F74" s="8"/>
-      <c r="H74" s="9"/>
-      <c r="I74" s="9"/>
-      <c r="J74" s="9"/>
-    </row>
-    <row r="75" spans="2:10" ht="10.5" customHeight="1">
-      <c r="B75" s="8"/>
-      <c r="C75" s="9"/>
-      <c r="D75" s="9"/>
-      <c r="E75" s="9"/>
-      <c r="F75" s="8"/>
-      <c r="H75" s="9"/>
-      <c r="I75" s="9"/>
-      <c r="J75" s="9"/>
-    </row>
-    <row r="76" spans="2:10" ht="10.5" customHeight="1">
-      <c r="J76" s="9"/>
-    </row>
-    <row r="77" spans="2:10" ht="10.5" customHeight="1">
-      <c r="J77" s="9"/>
-    </row>
-    <row r="78" spans="2:10" ht="10.5" customHeight="1">
-      <c r="J78" s="9"/>
-    </row>
-    <row r="79" spans="2:10" ht="10.5" customHeight="1">
-      <c r="J79" s="9"/>
-    </row>
-    <row r="80" spans="2:10" ht="10.5" customHeight="1">
-      <c r="J80" s="9"/>
-    </row>
-    <row r="81" spans="10:10" ht="10.5" customHeight="1">
-      <c r="J81" s="9"/>
-    </row>
-    <row r="82" spans="10:10" ht="10.5" customHeight="1">
-      <c r="J82" s="9"/>
-    </row>
-    <row r="83" spans="10:10" ht="10.5" customHeight="1">
-      <c r="J83" s="9"/>
-    </row>
-    <row r="84" spans="10:10" ht="10.5" customHeight="1">
-      <c r="J84" s="9"/>
-    </row>
-    <row r="85" spans="10:10" ht="10.5" customHeight="1">
-      <c r="J85" s="9"/>
-    </row>
-    <row r="86" spans="10:10" ht="10.5" customHeight="1">
-      <c r="J86" s="9"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -13082,7 +12618,7 @@
         <v>111</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>501</v>
+        <v>478</v>
       </c>
       <c r="E7" s="9">
         <v>2</v>
@@ -13095,7 +12631,7 @@
         <v>113</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>505</v>
+        <v>482</v>
       </c>
       <c r="J7" s="9"/>
     </row>
@@ -13108,7 +12644,7 @@
         <v>111</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>502</v>
+        <v>479</v>
       </c>
       <c r="E8" s="9">
         <v>3</v>
@@ -13121,7 +12657,7 @@
         <v>113</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>506</v>
+        <v>483</v>
       </c>
       <c r="J8" s="9"/>
     </row>
@@ -13134,7 +12670,7 @@
         <v>111</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>503</v>
+        <v>480</v>
       </c>
       <c r="E9" s="9">
         <v>4</v>
@@ -13147,7 +12683,7 @@
         <v>113</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>507</v>
+        <v>484</v>
       </c>
       <c r="J9" s="9"/>
     </row>
@@ -13160,7 +12696,7 @@
         <v>111</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>504</v>
+        <v>481</v>
       </c>
       <c r="E10" s="9">
         <v>5</v>
@@ -13173,7 +12709,7 @@
         <v>113</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>508</v>
+        <v>485</v>
       </c>
       <c r="J10" s="9"/>
     </row>
@@ -13943,7 +13479,7 @@
         <v>217</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="E7" s="9">
         <v>2</v>
@@ -14021,7 +13557,7 @@
         <v>218</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="E10" s="9">
         <v>1</v>
@@ -14096,7 +13632,7 @@
         <v>PACKAGE_BG_TYPE|0</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="D13" s="9" t="s">
         <v>41</v>
@@ -14109,7 +13645,7 @@
         <v>패키지 배경 | None</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="I13" s="9" t="s">
         <v>41</v>
@@ -14122,10 +13658,10 @@
         <v>PACKAGE_BG_TYPE|1</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="E14" s="9">
         <v>1</v>
@@ -14135,10 +13671,10 @@
         <v>패키지 배경 | 광고 제거 포함</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="J14" s="9"/>
     </row>
@@ -14148,10 +13684,10 @@
         <v>PACKAGE_BG_TYPE|2</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="E15" s="9">
         <v>2</v>
@@ -14161,10 +13697,10 @@
         <v>패키지 배경 | 일반 패키지 1</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="J15" s="9"/>
     </row>
@@ -14174,10 +13710,10 @@
         <v>PACKAGE_BG_TYPE|3</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="E16" s="9">
         <v>3</v>
@@ -14187,10 +13723,10 @@
         <v>패키지 배경 | 일반 패키지 2</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="J16" s="9"/>
     </row>
@@ -14200,10 +13736,10 @@
         <v>PACKAGE_BG_TYPE|4</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="E17" s="9">
         <v>4</v>
@@ -14213,10 +13749,10 @@
         <v>패키지 배경 | 일반 패키지 3</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="J17" s="9"/>
     </row>
@@ -14226,10 +13762,10 @@
         <v>PACKAGE_BG_TYPE|5</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>498</v>
+        <v>475</v>
       </c>
       <c r="E18" s="9">
         <v>5</v>
@@ -14239,10 +13775,10 @@
         <v>패키지 배경 | 버닝 번들 1</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>499</v>
+        <v>476</v>
       </c>
       <c r="J18" s="9"/>
     </row>
@@ -14255,7 +13791,7 @@
         <v>218</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="E19" s="9">
         <v>4</v>
@@ -14268,7 +13804,7 @@
         <v>227</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="J19" s="9"/>
     </row>
@@ -14278,7 +13814,7 @@
         <v>SPECIAL_OFFER_TYPE|0</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>445</v>
+        <v>430</v>
       </c>
       <c r="D20" s="9" t="s">
         <v>41</v>
@@ -14291,7 +13827,7 @@
         <v>스페셜 오퍼 타입 | None</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="I20" s="9" t="s">
         <v>41</v>
@@ -14304,10 +13840,10 @@
         <v>SPECIAL_OFFER_TYPE|1</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>445</v>
+        <v>430</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>455</v>
+        <v>440</v>
       </c>
       <c r="E21" s="9">
         <v>1</v>
@@ -14317,10 +13853,10 @@
         <v>스페셜 오퍼 타입 | 픽원 오퍼</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>456</v>
+        <v>441</v>
       </c>
       <c r="J21" s="9"/>
     </row>
@@ -14330,10 +13866,10 @@
         <v>SPECIAL_OFFER_TYPE|2</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>445</v>
+        <v>430</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="E22" s="9">
         <v>2</v>
@@ -14343,10 +13879,10 @@
         <v>스페셜 오퍼 타입 | 웰컴딜</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
       <c r="J22" s="9"/>
     </row>
@@ -14356,10 +13892,10 @@
         <v>SPECIAL_OFFER_TYPE|3</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>445</v>
+        <v>430</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>449</v>
+        <v>434</v>
       </c>
       <c r="E23" s="9">
         <v>3</v>
@@ -14369,10 +13905,10 @@
         <v>스페셜 오퍼 타입 | 엔드리스 오퍼</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>452</v>
+        <v>437</v>
       </c>
       <c r="J23" s="9"/>
     </row>
@@ -14382,10 +13918,10 @@
         <v>SPECIAL_OFFER_TYPE|4</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>445</v>
+        <v>430</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>527</v>
+        <v>504</v>
       </c>
       <c r="E24" s="9">
         <v>4</v>
@@ -14395,10 +13931,10 @@
         <v>스페셜 오퍼 타입 | 코인러쉬</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>526</v>
+        <v>503</v>
       </c>
       <c r="J24" s="9"/>
     </row>
@@ -14408,7 +13944,7 @@
         <v>PICKONE_OFFER_TYPE|0</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>457</v>
+        <v>442</v>
       </c>
       <c r="D25" s="9" t="s">
         <v>41</v>
@@ -14421,7 +13957,7 @@
         <v>픽원 오퍼 타입 | None</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>458</v>
+        <v>443</v>
       </c>
       <c r="I25" s="9" t="s">
         <v>41</v>
@@ -14434,10 +13970,10 @@
         <v>PICKONE_OFFER_TYPE|1</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>457</v>
+        <v>442</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>446</v>
+        <v>431</v>
       </c>
       <c r="E26" s="9">
         <v>1</v>
@@ -14447,10 +13983,10 @@
         <v>픽원 오퍼 타입 | 시즌1</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>458</v>
+        <v>443</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>461</v>
+        <v>446</v>
       </c>
       <c r="J26" s="9"/>
     </row>
@@ -14460,10 +13996,10 @@
         <v>PICKONE_OFFER_TYPE|2</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>457</v>
+        <v>442</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>450</v>
+        <v>435</v>
       </c>
       <c r="E27" s="9">
         <v>2</v>
@@ -14473,10 +14009,10 @@
         <v>픽원 오퍼 타입 | 시즌2</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>458</v>
+        <v>443</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>462</v>
+        <v>447</v>
       </c>
       <c r="J27" s="9"/>
     </row>
@@ -14486,10 +14022,10 @@
         <v>PICKONE_OFFER_TYPE|3</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>457</v>
+        <v>442</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>451</v>
+        <v>436</v>
       </c>
       <c r="E28" s="9">
         <v>3</v>
@@ -14499,10 +14035,10 @@
         <v>픽원 오퍼 타입 | 시즌3</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>458</v>
+        <v>443</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>463</v>
+        <v>448</v>
       </c>
       <c r="J28" s="9"/>
     </row>
@@ -14512,10 +14048,10 @@
         <v>PICKONE_OFFER_TYPE|4</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>457</v>
+        <v>442</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>475</v>
+        <v>452</v>
       </c>
       <c r="E29" s="9">
         <v>4</v>
@@ -14525,10 +14061,10 @@
         <v>픽원 오퍼 타입 | 시즌4</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>458</v>
+        <v>443</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>476</v>
+        <v>453</v>
       </c>
       <c r="J29" s="9"/>
     </row>
@@ -14538,10 +14074,10 @@
         <v>PICKONE_OFFER_TYPE|5</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>457</v>
+        <v>442</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>477</v>
+        <v>454</v>
       </c>
       <c r="E30" s="9">
         <v>5</v>
@@ -14551,10 +14087,10 @@
         <v>픽원 오퍼 타입 | 시즌5</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>458</v>
+        <v>443</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>478</v>
+        <v>455</v>
       </c>
       <c r="J30" s="9"/>
     </row>
@@ -14564,10 +14100,10 @@
         <v>PICKONE_OFFER_TYPE|6</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>457</v>
+        <v>442</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>509</v>
+        <v>486</v>
       </c>
       <c r="E31" s="9">
         <v>6</v>
@@ -14577,10 +14113,10 @@
         <v>픽원 오퍼 타입 | 시즌6</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>458</v>
+        <v>443</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>510</v>
+        <v>487</v>
       </c>
       <c r="J31" s="9"/>
     </row>
@@ -14590,10 +14126,10 @@
         <v>PICKONE_OFFER_TYPE|7</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>457</v>
+        <v>442</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>515</v>
+        <v>492</v>
       </c>
       <c r="E32" s="9">
         <v>7</v>
@@ -14603,10 +14139,10 @@
         <v>픽원 오퍼 타입 | 시즌7</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>458</v>
+        <v>443</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>516</v>
+        <v>493</v>
       </c>
       <c r="J32" s="9"/>
     </row>
@@ -14616,10 +14152,10 @@
         <v>PICKONE_OFFER_TYPE|8</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>457</v>
+        <v>442</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>517</v>
+        <v>494</v>
       </c>
       <c r="E33" s="9">
         <v>8</v>
@@ -14629,10 +14165,10 @@
         <v>픽원 오퍼 타입 | 시즌8</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>458</v>
+        <v>443</v>
       </c>
       <c r="I33" s="9" t="s">
-        <v>518</v>
+        <v>495</v>
       </c>
       <c r="J33" s="9"/>
     </row>
@@ -14642,10 +14178,10 @@
         <v>PICKONE_OFFER_TYPE|9</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>457</v>
+        <v>442</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>521</v>
+        <v>498</v>
       </c>
       <c r="E34" s="9">
         <v>9</v>
@@ -14655,10 +14191,10 @@
         <v>픽원 오퍼 타입 | 시즌9</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>458</v>
+        <v>443</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>522</v>
+        <v>499</v>
       </c>
       <c r="J34" s="9"/>
     </row>
@@ -14668,10 +14204,10 @@
         <v>PICKONE_OFFER_TYPE|10</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>457</v>
+        <v>442</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>544</v>
+        <v>521</v>
       </c>
       <c r="E35" s="9">
         <v>10</v>
@@ -14681,10 +14217,10 @@
         <v>픽원 오퍼 타입 | 시즌10</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>458</v>
+        <v>443</v>
       </c>
       <c r="I35" s="9" t="s">
-        <v>545</v>
+        <v>522</v>
       </c>
       <c r="J35" s="9"/>
     </row>
@@ -14694,7 +14230,7 @@
         <v>WELCOME_DEAL_TYPE|0</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>459</v>
+        <v>444</v>
       </c>
       <c r="D36" s="9" t="s">
         <v>41</v>
@@ -14707,7 +14243,7 @@
         <v>웰컴딜 타입 | None</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>460</v>
+        <v>445</v>
       </c>
       <c r="I36" s="9" t="s">
         <v>41</v>
@@ -14720,10 +14256,10 @@
         <v>WELCOME_DEAL_TYPE|1</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>459</v>
+        <v>444</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>447</v>
+        <v>432</v>
       </c>
       <c r="E37" s="9">
         <v>1</v>
@@ -14733,10 +14269,10 @@
         <v>웰컴딜 타입 | 시즌1</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>460</v>
+        <v>445</v>
       </c>
       <c r="I37" s="9" t="s">
-        <v>461</v>
+        <v>446</v>
       </c>
       <c r="J37" s="9"/>
     </row>
@@ -14746,10 +14282,10 @@
         <v>WELCOME_DEAL_TYPE|2</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>459</v>
+        <v>444</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>453</v>
+        <v>438</v>
       </c>
       <c r="E38" s="9">
         <v>2</v>
@@ -14759,10 +14295,10 @@
         <v>웰컴딜 타입 | 시즌2</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>460</v>
+        <v>445</v>
       </c>
       <c r="I38" s="9" t="s">
-        <v>462</v>
+        <v>447</v>
       </c>
       <c r="J38" s="9"/>
     </row>
@@ -14772,7 +14308,7 @@
         <v>ENDLESS_OFFER_TYPE|0</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>464</v>
+        <v>449</v>
       </c>
       <c r="D39" s="9" t="s">
         <v>41</v>
@@ -14785,7 +14321,7 @@
         <v>엔드리스 오퍼 | None</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>452</v>
+        <v>437</v>
       </c>
       <c r="I39" s="9" t="s">
         <v>41</v>
@@ -14798,10 +14334,10 @@
         <v>ENDLESS_OFFER_TYPE|1</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>464</v>
+        <v>449</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>454</v>
+        <v>439</v>
       </c>
       <c r="E40" s="9">
         <v>1</v>
@@ -14811,10 +14347,10 @@
         <v>엔드리스 오퍼 | 세로형 1</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>452</v>
+        <v>437</v>
       </c>
       <c r="I40" s="9" t="s">
-        <v>465</v>
+        <v>450</v>
       </c>
       <c r="J40" s="9"/>
     </row>
@@ -14824,10 +14360,10 @@
         <v>ENDLESS_OFFER_TYPE|2</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>464</v>
+        <v>449</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>448</v>
+        <v>433</v>
       </c>
       <c r="E41" s="9">
         <v>2</v>
@@ -14837,10 +14373,10 @@
         <v>엔드리스 오퍼 | 체인형 1</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>452</v>
+        <v>437</v>
       </c>
       <c r="I41" s="9" t="s">
-        <v>500</v>
+        <v>477</v>
       </c>
       <c r="J41" s="9"/>
     </row>
@@ -14850,10 +14386,10 @@
         <v>PACKAGE_BG_TYPE|6</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>512</v>
+        <v>489</v>
       </c>
       <c r="E42" s="9">
         <v>6</v>
@@ -14863,10 +14399,10 @@
         <v>패키지 배경 | 실패 번들</v>
       </c>
       <c r="H42" s="9" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="I42" s="9" t="s">
-        <v>511</v>
+        <v>488</v>
       </c>
       <c r="J42" s="9"/>
     </row>
@@ -14876,7 +14412,7 @@
         <v>COIN_RUSH_TYPE|0</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>523</v>
+        <v>500</v>
       </c>
       <c r="D43" s="9" t="s">
         <v>41</v>
@@ -14889,7 +14425,7 @@
         <v>코인 러쉬 타입 | None</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>524</v>
+        <v>501</v>
       </c>
       <c r="I43" s="9" t="s">
         <v>41</v>
@@ -14902,10 +14438,10 @@
         <v>COIN_RUSH_TYPE|1</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>523</v>
+        <v>500</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>525</v>
+        <v>502</v>
       </c>
       <c r="E44" s="9">
         <v>1</v>
@@ -14915,10 +14451,10 @@
         <v>코인 러쉬 타입 | 시즌1</v>
       </c>
       <c r="H44" s="9" t="s">
-        <v>524</v>
+        <v>501</v>
       </c>
       <c r="I44" s="9" t="s">
-        <v>461</v>
+        <v>446</v>
       </c>
       <c r="J44" s="9"/>
     </row>
@@ -15135,10 +14671,10 @@
         <v>EVENT_TYPE|0</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="E5" s="9">
         <v>0</v>
@@ -15148,10 +14684,10 @@
         <v>이벤트 타입 | 블록 패스</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="J5" s="9"/>
     </row>
@@ -15161,10 +14697,10 @@
         <v>EVENT_TYPE|1</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="E6" s="9">
         <v>1</v>
@@ -15174,10 +14710,10 @@
         <v>이벤트 타입 | 팩토리 채스</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="J6" s="9"/>
     </row>
@@ -15187,10 +14723,10 @@
         <v>EVENT_TYPE|2</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>513</v>
+        <v>490</v>
       </c>
       <c r="E7" s="9">
         <v>2</v>
@@ -15200,10 +14736,10 @@
         <v>이벤트 타입 | 어드벤어스트릭</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>514</v>
+        <v>491</v>
       </c>
       <c r="J7" s="9"/>
     </row>
@@ -15213,10 +14749,10 @@
         <v>EVENT_TYPE|3</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>519</v>
+        <v>496</v>
       </c>
       <c r="E8" s="9">
         <v>3</v>
@@ -15226,10 +14762,10 @@
         <v>이벤트 타입 | 피냐타 파티</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>520</v>
+        <v>497</v>
       </c>
       <c r="J8" s="9"/>
     </row>
@@ -15239,10 +14775,10 @@
         <v>EVENT_TYPE|4</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>542</v>
+        <v>519</v>
       </c>
       <c r="E9" s="9">
         <v>4</v>
@@ -15252,10 +14788,10 @@
         <v>이벤트 타입 | 윈타워</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>543</v>
+        <v>520</v>
       </c>
       <c r="J9" s="9"/>
     </row>
